--- a/AAII_Financials/Quarterly/FFBW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FFBW_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
   <si>
     <t>FFBW</t>
   </si>
@@ -656,169 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="F7" s="2">
         <v>44834</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44469</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44286</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44104</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43921</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43738</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43646</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43555</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43465</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43373</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43281</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43190</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43008</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42916</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42825</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42735</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3">
         <v>3200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>3000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2700</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J8" s="3">
-        <v>3200</v>
       </c>
       <c r="K8" s="3">
         <v>2800</v>
       </c>
       <c r="L8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N8" s="3">
         <v>2700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>5600</v>
-      </c>
-      <c r="N8" s="3">
-        <v>2800</v>
-      </c>
-      <c r="O8" s="3">
-        <v>2900</v>
       </c>
       <c r="P8" s="3">
         <v>2800</v>
       </c>
       <c r="Q8" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="R8" s="3">
         <v>2800</v>
@@ -827,34 +835,40 @@
         <v>2800</v>
       </c>
       <c r="T8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="U8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="V8" s="3">
         <v>2700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2700</v>
-      </c>
-      <c r="V8" s="3">
-        <v>2300</v>
-      </c>
-      <c r="W8" s="3">
-        <v>2400</v>
       </c>
       <c r="X8" s="3">
         <v>2300</v>
       </c>
       <c r="Y8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AA8" s="3">
         <v>2200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>2100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>2100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -933,8 +947,14 @@
       <c r="AB9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1013,8 +1033,14 @@
       <c r="AB10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,8 +1069,10 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1123,8 +1151,14 @@
       <c r="AB12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,8 +1237,14 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1283,8 +1323,14 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1363,8 +1409,14 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,19 +1442,21 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3">
         <v>300</v>
-      </c>
-      <c r="E17" s="3">
-        <v>200</v>
-      </c>
-      <c r="F17" s="3">
-        <v>200</v>
       </c>
       <c r="G17" s="3">
         <v>200</v>
@@ -1411,46 +1465,46 @@
         <v>200</v>
       </c>
       <c r="I17" s="3">
+        <v>200</v>
+      </c>
+      <c r="J17" s="3">
+        <v>200</v>
+      </c>
+      <c r="K17" s="3">
         <v>300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>700</v>
-      </c>
-      <c r="P17" s="3">
-        <v>800</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>800</v>
       </c>
       <c r="R17" s="3">
         <v>800</v>
       </c>
       <c r="S17" s="3">
+        <v>800</v>
+      </c>
+      <c r="T17" s="3">
+        <v>800</v>
+      </c>
+      <c r="U17" s="3">
         <v>700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>700</v>
-      </c>
-      <c r="U17" s="3">
-        <v>600</v>
-      </c>
-      <c r="V17" s="3">
-        <v>500</v>
       </c>
       <c r="W17" s="3">
         <v>600</v>
@@ -1459,69 +1513,75 @@
         <v>500</v>
       </c>
       <c r="Y17" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA17" s="3">
         <v>400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3">
         <v>2900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>2800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>2600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H18" s="3">
-        <v>2500</v>
       </c>
       <c r="I18" s="3">
         <v>2500</v>
       </c>
       <c r="J18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L18" s="3">
         <v>2900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>4400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>2200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>2200</v>
-      </c>
-      <c r="P18" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>2000</v>
       </c>
       <c r="R18" s="3">
         <v>2000</v>
       </c>
       <c r="S18" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="T18" s="3">
         <v>2000</v>
@@ -1530,10 +1590,10 @@
         <v>2100</v>
       </c>
       <c r="V18" s="3">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="W18" s="3">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="X18" s="3">
         <v>1800</v>
@@ -1542,16 +1602,22 @@
         <v>1800</v>
       </c>
       <c r="Z18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AB18" s="3">
         <v>1700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>1200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,168 +1646,182 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-1900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-1800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-2000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-3300</v>
       </c>
       <c r="N20" s="3">
         <v>-1700</v>
       </c>
       <c r="O20" s="3">
-        <v>-1500</v>
+        <v>-3300</v>
       </c>
       <c r="P20" s="3">
-        <v>-1500</v>
+        <v>-1700</v>
       </c>
       <c r="Q20" s="3">
         <v>-1500</v>
       </c>
       <c r="R20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="T20" s="3">
         <v>-1700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-1800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-1500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-1600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-1900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="3">
+        <v>900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>700</v>
+      </c>
+      <c r="J21" s="3">
         <v>800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="K21" s="3">
+        <v>600</v>
+      </c>
+      <c r="L21" s="3">
         <v>900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="M21" s="3">
         <v>800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="N21" s="3">
         <v>700</v>
       </c>
-      <c r="H21" s="3">
-        <v>700</v>
-      </c>
-      <c r="I21" s="3">
-        <v>600</v>
-      </c>
-      <c r="J21" s="3">
-        <v>900</v>
-      </c>
-      <c r="K21" s="3">
-        <v>800</v>
-      </c>
-      <c r="L21" s="3">
-        <v>700</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1200</v>
-      </c>
-      <c r="N21" s="3">
-        <v>600</v>
-      </c>
-      <c r="O21" s="3">
-        <v>800</v>
       </c>
       <c r="P21" s="3">
         <v>600</v>
       </c>
       <c r="Q21" s="3">
+        <v>800</v>
+      </c>
+      <c r="R21" s="3">
         <v>600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
+        <v>600</v>
+      </c>
+      <c r="T21" s="3">
         <v>400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-400</v>
       </c>
-      <c r="AB21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1820,88 +1900,100 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>600</v>
+      </c>
+      <c r="F23" s="3">
         <v>700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>600</v>
-      </c>
-      <c r="H23" s="3">
-        <v>600</v>
       </c>
       <c r="I23" s="3">
         <v>600</v>
       </c>
       <c r="J23" s="3">
+        <v>600</v>
+      </c>
+      <c r="K23" s="3">
+        <v>600</v>
+      </c>
+      <c r="L23" s="3">
         <v>900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1100</v>
-      </c>
-      <c r="N23" s="3">
-        <v>500</v>
-      </c>
-      <c r="O23" s="3">
-        <v>700</v>
       </c>
       <c r="P23" s="3">
         <v>500</v>
       </c>
       <c r="Q23" s="3">
+        <v>700</v>
+      </c>
+      <c r="R23" s="3">
         <v>500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
+        <v>500</v>
+      </c>
+      <c r="T23" s="3">
         <v>300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
         <v>100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1918,19 +2010,19 @@
         <v>200</v>
       </c>
       <c r="H24" s="3">
+        <v>200</v>
+      </c>
+      <c r="I24" s="3">
+        <v>200</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
-      </c>
-      <c r="K24" s="3">
-        <v>200</v>
-      </c>
-      <c r="L24" s="3">
-        <v>100</v>
       </c>
       <c r="M24" s="3">
         <v>200</v>
@@ -1945,7 +2037,7 @@
         <v>100</v>
       </c>
       <c r="Q24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R24" s="3">
         <v>100</v>
@@ -1963,25 +2055,31 @@
         <v>100</v>
       </c>
       <c r="W24" s="3">
+        <v>100</v>
+      </c>
+      <c r="X24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2158,186 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3">
         <v>500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>500</v>
-      </c>
-      <c r="I26" s="3">
-        <v>500</v>
-      </c>
-      <c r="J26" s="3">
-        <v>700</v>
       </c>
       <c r="K26" s="3">
         <v>500</v>
       </c>
       <c r="L26" s="3">
+        <v>700</v>
+      </c>
+      <c r="M26" s="3">
         <v>500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
+        <v>500</v>
+      </c>
+      <c r="O26" s="3">
         <v>800</v>
-      </c>
-      <c r="N26" s="3">
-        <v>400</v>
-      </c>
-      <c r="O26" s="3">
-        <v>500</v>
       </c>
       <c r="P26" s="3">
         <v>400</v>
       </c>
       <c r="Q26" s="3">
+        <v>500</v>
+      </c>
+      <c r="R26" s="3">
         <v>400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
+        <v>400</v>
+      </c>
+      <c r="T26" s="3">
         <v>200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-100</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
         <v>100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-300</v>
       </c>
-      <c r="AB26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3">
         <v>500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>500</v>
-      </c>
-      <c r="I27" s="3">
-        <v>500</v>
-      </c>
-      <c r="J27" s="3">
-        <v>700</v>
       </c>
       <c r="K27" s="3">
         <v>500</v>
       </c>
       <c r="L27" s="3">
+        <v>700</v>
+      </c>
+      <c r="M27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
+        <v>500</v>
+      </c>
+      <c r="O27" s="3">
         <v>800</v>
-      </c>
-      <c r="N27" s="3">
-        <v>400</v>
-      </c>
-      <c r="O27" s="3">
-        <v>500</v>
       </c>
       <c r="P27" s="3">
         <v>400</v>
       </c>
       <c r="Q27" s="3">
+        <v>500</v>
+      </c>
+      <c r="R27" s="3">
         <v>400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
+        <v>400</v>
+      </c>
+      <c r="T27" s="3">
         <v>200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-100</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-300</v>
       </c>
-      <c r="AB27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2416,14 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2344,33 +2466,33 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-400</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2380,8 +2502,14 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2588,14 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2674,186 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
         <v>2200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>1900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>1800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>2000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>1600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>1700</v>
-      </c>
-      <c r="M32" s="3">
-        <v>3300</v>
       </c>
       <c r="N32" s="3">
         <v>1700</v>
       </c>
       <c r="O32" s="3">
-        <v>1500</v>
+        <v>3300</v>
       </c>
       <c r="P32" s="3">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="Q32" s="3">
         <v>1500</v>
       </c>
       <c r="R32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T32" s="3">
         <v>1700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>1800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>1500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>1600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>1900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>1800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>1600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>1600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>1700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3">
         <v>500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>500</v>
-      </c>
-      <c r="I33" s="3">
-        <v>500</v>
-      </c>
-      <c r="J33" s="3">
-        <v>700</v>
       </c>
       <c r="K33" s="3">
         <v>500</v>
       </c>
       <c r="L33" s="3">
+        <v>700</v>
+      </c>
+      <c r="M33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
+        <v>500</v>
+      </c>
+      <c r="O33" s="3">
         <v>800</v>
-      </c>
-      <c r="N33" s="3">
-        <v>400</v>
-      </c>
-      <c r="O33" s="3">
-        <v>500</v>
       </c>
       <c r="P33" s="3">
         <v>400</v>
       </c>
       <c r="Q33" s="3">
+        <v>500</v>
+      </c>
+      <c r="R33" s="3">
         <v>400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
+        <v>400</v>
+      </c>
+      <c r="T33" s="3">
         <v>200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-400</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
         <v>100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-300</v>
       </c>
-      <c r="AB33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2932,191 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3">
         <v>500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>500</v>
-      </c>
-      <c r="I35" s="3">
-        <v>500</v>
-      </c>
-      <c r="J35" s="3">
-        <v>700</v>
       </c>
       <c r="K35" s="3">
         <v>500</v>
       </c>
       <c r="L35" s="3">
+        <v>700</v>
+      </c>
+      <c r="M35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
+        <v>500</v>
+      </c>
+      <c r="O35" s="3">
         <v>800</v>
-      </c>
-      <c r="N35" s="3">
-        <v>400</v>
-      </c>
-      <c r="O35" s="3">
-        <v>500</v>
       </c>
       <c r="P35" s="3">
         <v>400</v>
       </c>
       <c r="Q35" s="3">
+        <v>500</v>
+      </c>
+      <c r="R35" s="3">
         <v>400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
+        <v>400</v>
+      </c>
+      <c r="T35" s="3">
         <v>200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-400</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
         <v>100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-300</v>
       </c>
-      <c r="AB35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="F38" s="2">
         <v>44834</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44469</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44286</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44104</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43921</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43738</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43646</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43555</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43465</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43373</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43281</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43190</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43008</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42916</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42825</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42735</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3145,10 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,168 +3177,182 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F41" s="3">
         <v>15700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>30900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>38500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>52500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>71000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>62000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>50700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>41500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>5300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>11000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>4100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>4200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>3400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>3300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>5800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>5000</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" s="3">
         <v>2300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>13400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>18400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>16600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>11600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>25600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>13900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>9200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>3700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>18200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>5400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>37100</v>
-      </c>
-      <c r="P42" s="3">
-        <v>2300</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>3200</v>
       </c>
       <c r="R42" s="3">
         <v>2300</v>
       </c>
       <c r="S42" s="3">
+        <v>3200</v>
+      </c>
+      <c r="T42" s="3">
+        <v>2300</v>
+      </c>
+      <c r="U42" s="3">
         <v>3500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>1300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>1100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>11000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>13000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>33700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>3500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>2000</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB42" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3245,8 +3431,14 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3325,8 +3517,14 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3405,8 +3603,14 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3485,8 +3689,14 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3565,88 +3775,100 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F48" s="3">
         <v>6700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>5900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>5600</v>
-      </c>
-      <c r="G48" s="3">
-        <v>5500</v>
-      </c>
-      <c r="H48" s="3">
-        <v>5500</v>
       </c>
       <c r="I48" s="3">
         <v>5500</v>
       </c>
       <c r="J48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="L48" s="3">
         <v>5600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>5600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>4800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>4800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>4900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>5000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>5100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>5100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>5200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>5200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>5300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>7300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>7600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>7700</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3725,8 +3947,14 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +4033,14 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,8 +4119,14 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3965,8 +4205,14 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4291,100 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>332000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>333100</v>
+      </c>
+      <c r="F54" s="3">
         <v>313800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>330400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>341700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>357100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>355300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>352600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>337800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>339000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>285800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>293400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>278000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>292200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>258100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>258300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>259600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>262700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>268300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>265900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>260600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>256500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>270300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>236200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>236100</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4413,10 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,88 +4445,96 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>100</v>
-      </c>
-      <c r="E57" s="3">
-        <v>100</v>
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H57" s="3">
+        <v>100</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
-      </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3">
         <v>500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>200</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4345,8 +4613,14 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4425,8 +4699,14 @@
       <c r="AB59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4505,8 +4785,14 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4585,8 +4871,14 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4665,8 +4957,14 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +5043,14 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +5129,14 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5215,100 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66" s="3">
+        <v>257500</v>
+      </c>
+      <c r="F66" s="3">
         <v>236300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>246600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>254500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>263100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>259500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>255800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>238700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>235700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>183100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>191400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>177000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>230300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>196800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>197100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>198700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>202400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>208800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>206600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>201600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>197000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>235900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>201800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>202000</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5337,10 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5419,14 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5505,14 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5591,14 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5677,100 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3">
         <v>42100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>41600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>40900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>40400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>40000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>39500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>39100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>38400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>37900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>37300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>37000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>36600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>36000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>35600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>35200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>35000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>34800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>34400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>34100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>33900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>34400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>34300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>34200</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5849,14 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5935,14 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +6021,100 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>75400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>75500</v>
+      </c>
+      <c r="F76" s="3">
         <v>77500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>83900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>87200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>94000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>95800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>96800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>99100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>103300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>102600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>102000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>101000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>61900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>61300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>61200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>60800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>60400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>59500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>59300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>59000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>59500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>34400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>34300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>34200</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6193,191 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="F80" s="2">
         <v>44834</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44469</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44286</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44104</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43921</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43738</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43646</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43555</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43465</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43373</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43281</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43190</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43008</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42916</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42825</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42735</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3">
         <v>500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>500</v>
-      </c>
-      <c r="I81" s="3">
-        <v>500</v>
-      </c>
-      <c r="J81" s="3">
-        <v>700</v>
       </c>
       <c r="K81" s="3">
         <v>500</v>
       </c>
       <c r="L81" s="3">
+        <v>700</v>
+      </c>
+      <c r="M81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
+        <v>500</v>
+      </c>
+      <c r="O81" s="3">
         <v>800</v>
-      </c>
-      <c r="N81" s="3">
-        <v>400</v>
-      </c>
-      <c r="O81" s="3">
-        <v>500</v>
       </c>
       <c r="P81" s="3">
         <v>400</v>
       </c>
       <c r="Q81" s="3">
+        <v>500</v>
+      </c>
+      <c r="R81" s="3">
         <v>400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
+        <v>400</v>
+      </c>
+      <c r="T81" s="3">
         <v>200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-400</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
         <v>100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-300</v>
       </c>
-      <c r="AB81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,31 +6406,33 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>100</v>
-      </c>
-      <c r="E83" s="3">
-        <v>100</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
@@ -6043,13 +6441,13 @@
         <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
       </c>
       <c r="O83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
@@ -6090,8 +6488,14 @@
       <c r="AB83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6574,14 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6660,14 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6746,14 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6832,14 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6918,100 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G89" s="3">
         <v>900</v>
       </c>
-      <c r="E89" s="3">
-        <v>900</v>
-      </c>
-      <c r="F89" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K89" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L89" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N89" s="3">
         <v>1000</v>
       </c>
-      <c r="I89" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J89" s="3">
-        <v>2000</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>800</v>
+      </c>
+      <c r="R89" s="3">
+        <v>100</v>
+      </c>
+      <c r="S89" s="3">
+        <v>300</v>
+      </c>
+      <c r="T89" s="3">
+        <v>1500</v>
+      </c>
+      <c r="U89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V89" s="3">
+        <v>600</v>
+      </c>
+      <c r="W89" s="3">
         <v>1000</v>
       </c>
-      <c r="M89" s="3">
-        <v>1100</v>
-      </c>
-      <c r="N89" s="3">
-        <v>1100</v>
-      </c>
-      <c r="O89" s="3">
-        <v>800</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="X89" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y89" s="3">
         <v>100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Z89" s="3">
         <v>300</v>
       </c>
-      <c r="R89" s="3">
-        <v>1500</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T89" s="3">
-        <v>600</v>
-      </c>
-      <c r="U89" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="AA89" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB89" s="3">
         <v>500</v>
       </c>
-      <c r="W89" s="3">
-        <v>100</v>
-      </c>
-      <c r="X89" s="3">
-        <v>300</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>500</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,8 +7040,10 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6639,14 +7081,14 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -6663,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -6672,16 +7114,22 @@
         <v>-100</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +7208,14 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7294,100 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-11400</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="G94" s="3">
         <v>-2300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="J94" s="3">
+        <v>19100</v>
+      </c>
+      <c r="K94" s="3">
+        <v>9600</v>
+      </c>
+      <c r="L94" s="3">
+        <v>17000</v>
+      </c>
+      <c r="M94" s="3">
+        <v>38400</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="O94" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="P94" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>300</v>
+      </c>
+      <c r="R94" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="S94" s="3">
+        <v>6200</v>
+      </c>
+      <c r="T94" s="3">
         <v>800</v>
       </c>
-      <c r="G94" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="I94" s="3">
-        <v>9600</v>
-      </c>
-      <c r="J94" s="3">
-        <v>17000</v>
-      </c>
-      <c r="K94" s="3">
-        <v>38400</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-19300</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="O94" s="3">
-        <v>300</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>6200</v>
-      </c>
-      <c r="R94" s="3">
-        <v>800</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>6700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-12700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-7700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-8000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>3100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7416,10 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7030,8 +7498,14 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7584,14 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7670,14 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,88 +7756,100 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="I100" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J100" s="3">
+        <v>14900</v>
+      </c>
+      <c r="K100" s="3">
+        <v>14000</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="O100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="P100" s="3">
         <v>-15800</v>
       </c>
-      <c r="E100" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="G100" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H100" s="3">
-        <v>2200</v>
-      </c>
-      <c r="I100" s="3">
-        <v>14000</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-15800</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>34100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-3600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-4200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-6100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>1900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>4900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>4600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-12600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>33600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7430,84 +7928,96 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>-26300</v>
-      </c>
-      <c r="E102" s="3">
+      <c r="D102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="G102" s="3">
         <v>-12400</v>
       </c>
-      <c r="F102" s="3">
-        <v>-12300</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="I102" s="3">
         <v>-13100</v>
       </c>
-      <c r="H102" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
+        <v>38600</v>
+      </c>
+      <c r="K102" s="3">
         <v>25300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>17600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>34000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-12200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-19800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-24500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>35200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>2800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-6800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-2600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-20400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>26400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-2200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FFBW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FFBW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
   <si>
     <t>FFBW</t>
   </si>
@@ -656,183 +656,189 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
+      <c r="D8" s="3">
+        <v>15500</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I8" s="3">
         <v>3200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="J8" s="3">
         <v>3000</v>
       </c>
-      <c r="H8" s="3">
-        <v>2800</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2700</v>
-      </c>
-      <c r="K8" s="3">
-        <v>2800</v>
-      </c>
-      <c r="L8" s="3">
-        <v>3200</v>
       </c>
       <c r="M8" s="3">
         <v>2800</v>
       </c>
       <c r="N8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="O8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="P8" s="3">
         <v>2700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>5600</v>
-      </c>
-      <c r="P8" s="3">
-        <v>2800</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>2900</v>
       </c>
       <c r="R8" s="3">
         <v>2800</v>
       </c>
       <c r="S8" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="T8" s="3">
         <v>2800</v>
@@ -841,34 +847,40 @@
         <v>2800</v>
       </c>
       <c r="V8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="W8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="X8" s="3">
         <v>2700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2700</v>
-      </c>
-      <c r="X8" s="3">
-        <v>2300</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>2400</v>
       </c>
       <c r="Z8" s="3">
         <v>2300</v>
       </c>
       <c r="AA8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AC8" s="3">
         <v>2200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>2100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -953,8 +965,14 @@
       <c r="AD9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1039,8 +1057,14 @@
       <c r="AD10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,8 +1095,10 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1157,8 +1183,14 @@
       <c r="AD12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,8 +1275,14 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1329,8 +1367,14 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1415,8 +1459,14 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,73 +1494,75 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>5</v>
+      <c r="D17" s="3">
+        <v>4700</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3">
+        <v>800</v>
+      </c>
+      <c r="H17" s="3">
+        <v>400</v>
+      </c>
+      <c r="I17" s="3">
         <v>300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>200</v>
-      </c>
-      <c r="I17" s="3">
-        <v>200</v>
       </c>
       <c r="J17" s="3">
         <v>200</v>
       </c>
       <c r="K17" s="3">
+        <v>200</v>
+      </c>
+      <c r="L17" s="3">
+        <v>200</v>
+      </c>
+      <c r="M17" s="3">
         <v>300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>700</v>
-      </c>
-      <c r="R17" s="3">
-        <v>800</v>
-      </c>
-      <c r="S17" s="3">
-        <v>800</v>
       </c>
       <c r="T17" s="3">
         <v>800</v>
       </c>
       <c r="U17" s="3">
+        <v>800</v>
+      </c>
+      <c r="V17" s="3">
+        <v>800</v>
+      </c>
+      <c r="W17" s="3">
         <v>700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>700</v>
-      </c>
-      <c r="W17" s="3">
-        <v>600</v>
-      </c>
-      <c r="X17" s="3">
-        <v>500</v>
       </c>
       <c r="Y17" s="3">
         <v>600</v>
@@ -1519,75 +1571,81 @@
         <v>500</v>
       </c>
       <c r="AA17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC17" s="3">
         <v>400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
+      <c r="D18" s="3">
+        <v>10800</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="3">
-        <v>2900</v>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G18" s="3">
         <v>2800</v>
       </c>
       <c r="H18" s="3">
-        <v>2600</v>
+        <v>3000</v>
       </c>
       <c r="I18" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="J18" s="3">
-        <v>2500</v>
+        <v>2800</v>
       </c>
       <c r="K18" s="3">
         <v>2500</v>
       </c>
       <c r="L18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N18" s="3">
         <v>2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>2300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>2300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>4400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>2200</v>
-      </c>
-      <c r="R18" s="3">
-        <v>2000</v>
-      </c>
-      <c r="S18" s="3">
-        <v>2000</v>
       </c>
       <c r="T18" s="3">
         <v>2000</v>
       </c>
       <c r="U18" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="V18" s="3">
         <v>2000</v>
@@ -1596,10 +1654,10 @@
         <v>2100</v>
       </c>
       <c r="X18" s="3">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="Y18" s="3">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="Z18" s="3">
         <v>1800</v>
@@ -1608,16 +1666,22 @@
         <v>1800</v>
       </c>
       <c r="AB18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AD18" s="3">
         <v>1700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>1200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,94 +1712,102 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>-8400</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3">
         <v>-2200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-1900</v>
-      </c>
       <c r="H20" s="3">
-        <v>-1800</v>
+        <v>-2100</v>
       </c>
       <c r="I20" s="3">
-        <v>-1800</v>
+        <v>-2200</v>
       </c>
       <c r="J20" s="3">
         <v>-1900</v>
       </c>
       <c r="K20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-3300</v>
       </c>
       <c r="P20" s="3">
         <v>-1700</v>
       </c>
       <c r="Q20" s="3">
-        <v>-1500</v>
+        <v>-3300</v>
       </c>
       <c r="R20" s="3">
-        <v>-1500</v>
+        <v>-1700</v>
       </c>
       <c r="S20" s="3">
         <v>-1500</v>
       </c>
       <c r="T20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="V20" s="3">
         <v>-1700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-1500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-1600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1745,83 +1817,89 @@
       <c r="E21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3">
         <v>900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
+        <v>800</v>
+      </c>
+      <c r="J21" s="3">
         <v>900</v>
       </c>
-      <c r="H21" s="3">
-        <v>500</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1200</v>
-      </c>
-      <c r="P21" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>800</v>
       </c>
       <c r="R21" s="3">
         <v>600</v>
       </c>
       <c r="S21" s="3">
+        <v>800</v>
+      </c>
+      <c r="T21" s="3">
         <v>600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
+        <v>600</v>
+      </c>
+      <c r="V21" s="3">
         <v>400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-400</v>
       </c>
-      <c r="AD21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1906,102 +1984,114 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="E23" s="3">
         <v>600</v>
       </c>
       <c r="F23" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G23" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="H23" s="3">
         <v>800</v>
       </c>
       <c r="I23" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="J23" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="K23" s="3">
         <v>600</v>
       </c>
       <c r="L23" s="3">
+        <v>600</v>
+      </c>
+      <c r="M23" s="3">
+        <v>600</v>
+      </c>
+      <c r="N23" s="3">
         <v>900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1100</v>
-      </c>
-      <c r="P23" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>700</v>
       </c>
       <c r="R23" s="3">
         <v>500</v>
       </c>
       <c r="S23" s="3">
+        <v>700</v>
+      </c>
+      <c r="T23" s="3">
         <v>500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
+        <v>500</v>
+      </c>
+      <c r="V23" s="3">
         <v>300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-200</v>
       </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3">
         <v>100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="E24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>200</v>
@@ -2016,19 +2106,19 @@
         <v>200</v>
       </c>
       <c r="J24" s="3">
+        <v>200</v>
+      </c>
+      <c r="K24" s="3">
+        <v>200</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
-      </c>
-      <c r="M24" s="3">
-        <v>200</v>
-      </c>
-      <c r="N24" s="3">
-        <v>100</v>
       </c>
       <c r="O24" s="3">
         <v>200</v>
@@ -2043,7 +2133,7 @@
         <v>100</v>
       </c>
       <c r="S24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T24" s="3">
         <v>100</v>
@@ -2061,25 +2151,31 @@
         <v>100</v>
       </c>
       <c r="Y24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-100</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2260,198 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
+      <c r="D26" s="3">
+        <v>1500</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3">
         <v>500</v>
-      </c>
-      <c r="G26" s="3">
-        <v>600</v>
       </c>
       <c r="H26" s="3">
         <v>600</v>
       </c>
       <c r="I26" s="3">
+        <v>500</v>
+      </c>
+      <c r="J26" s="3">
+        <v>600</v>
+      </c>
+      <c r="K26" s="3">
         <v>400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>500</v>
-      </c>
-      <c r="K26" s="3">
-        <v>500</v>
-      </c>
-      <c r="L26" s="3">
-        <v>700</v>
       </c>
       <c r="M26" s="3">
         <v>500</v>
       </c>
       <c r="N26" s="3">
+        <v>700</v>
+      </c>
+      <c r="O26" s="3">
         <v>500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q26" s="3">
         <v>800</v>
-      </c>
-      <c r="P26" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>500</v>
       </c>
       <c r="R26" s="3">
         <v>400</v>
       </c>
       <c r="S26" s="3">
+        <v>500</v>
+      </c>
+      <c r="T26" s="3">
         <v>400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
+        <v>400</v>
+      </c>
+      <c r="V26" s="3">
         <v>200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="3">
         <v>100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-300</v>
       </c>
-      <c r="AD26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
+      <c r="D27" s="3">
+        <v>1500</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3">
         <v>500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>600</v>
       </c>
       <c r="H27" s="3">
         <v>600</v>
       </c>
       <c r="I27" s="3">
+        <v>500</v>
+      </c>
+      <c r="J27" s="3">
+        <v>600</v>
+      </c>
+      <c r="K27" s="3">
         <v>400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>500</v>
-      </c>
-      <c r="K27" s="3">
-        <v>500</v>
-      </c>
-      <c r="L27" s="3">
-        <v>700</v>
       </c>
       <c r="M27" s="3">
         <v>500</v>
       </c>
       <c r="N27" s="3">
+        <v>700</v>
+      </c>
+      <c r="O27" s="3">
         <v>500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q27" s="3">
         <v>800</v>
-      </c>
-      <c r="P27" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>500</v>
       </c>
       <c r="R27" s="3">
         <v>400</v>
       </c>
       <c r="S27" s="3">
+        <v>500</v>
+      </c>
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
+        <v>400</v>
+      </c>
+      <c r="V27" s="3">
         <v>200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-100</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="3">
         <v>100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-300</v>
       </c>
-      <c r="AD27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2536,14 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2472,33 +2592,33 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-400</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2508,8 +2628,14 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2720,14 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,180 +2812,198 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>8400</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3">
         <v>2200</v>
       </c>
-      <c r="G32" s="3">
-        <v>1900</v>
-      </c>
       <c r="H32" s="3">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="I32" s="3">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="J32" s="3">
         <v>1900</v>
       </c>
       <c r="K32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>1600</v>
-      </c>
-      <c r="N32" s="3">
-        <v>1700</v>
-      </c>
-      <c r="O32" s="3">
-        <v>3300</v>
       </c>
       <c r="P32" s="3">
         <v>1700</v>
       </c>
       <c r="Q32" s="3">
-        <v>1500</v>
+        <v>3300</v>
       </c>
       <c r="R32" s="3">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="S32" s="3">
         <v>1500</v>
       </c>
       <c r="T32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="U32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="V32" s="3">
         <v>1700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>1500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>1600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>1600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>1900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>1600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>1600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>1700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
+      <c r="D33" s="3">
+        <v>1500</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3">
         <v>500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>600</v>
       </c>
       <c r="H33" s="3">
         <v>600</v>
       </c>
       <c r="I33" s="3">
+        <v>500</v>
+      </c>
+      <c r="J33" s="3">
+        <v>600</v>
+      </c>
+      <c r="K33" s="3">
         <v>400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>500</v>
-      </c>
-      <c r="K33" s="3">
-        <v>500</v>
-      </c>
-      <c r="L33" s="3">
-        <v>700</v>
       </c>
       <c r="M33" s="3">
         <v>500</v>
       </c>
       <c r="N33" s="3">
+        <v>700</v>
+      </c>
+      <c r="O33" s="3">
         <v>500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q33" s="3">
         <v>800</v>
-      </c>
-      <c r="P33" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>500</v>
       </c>
       <c r="R33" s="3">
         <v>400</v>
       </c>
       <c r="S33" s="3">
+        <v>500</v>
+      </c>
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
+        <v>400</v>
+      </c>
+      <c r="V33" s="3">
         <v>200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-400</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="3">
         <v>100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-300</v>
       </c>
-      <c r="AD33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3088,203 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
+      <c r="D35" s="3">
+        <v>1500</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3">
         <v>500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>600</v>
       </c>
       <c r="H35" s="3">
         <v>600</v>
       </c>
       <c r="I35" s="3">
+        <v>500</v>
+      </c>
+      <c r="J35" s="3">
+        <v>600</v>
+      </c>
+      <c r="K35" s="3">
         <v>400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>500</v>
-      </c>
-      <c r="K35" s="3">
-        <v>500</v>
-      </c>
-      <c r="L35" s="3">
-        <v>700</v>
       </c>
       <c r="M35" s="3">
         <v>500</v>
       </c>
       <c r="N35" s="3">
+        <v>700</v>
+      </c>
+      <c r="O35" s="3">
         <v>500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q35" s="3">
         <v>800</v>
-      </c>
-      <c r="P35" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>500</v>
       </c>
       <c r="R35" s="3">
         <v>400</v>
       </c>
       <c r="S35" s="3">
+        <v>500</v>
+      </c>
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
+        <v>400</v>
+      </c>
+      <c r="V35" s="3">
         <v>200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-400</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="3">
         <v>100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-300</v>
       </c>
-      <c r="AD35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3315,10 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,180 +3349,194 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>5</v>
+      <c r="D41" s="3">
+        <v>5800</v>
       </c>
       <c r="E41" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F41" s="3">
+        <v>9800</v>
+      </c>
+      <c r="G41" s="3">
         <v>11400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
+        <v>10900</v>
+      </c>
+      <c r="I41" s="3">
         <v>15700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>30900</v>
       </c>
-      <c r="H41" s="3">
-        <v>38500</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>52500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>71000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>62000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>50700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>41500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>11000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>4200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>4400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>3400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>2400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>3300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>5800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>5000</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>5</v>
+      <c r="D42" s="3">
+        <v>1800</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H42" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I42" s="3">
         <v>2300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="J42" s="3">
         <v>13400</v>
       </c>
-      <c r="H42" s="3">
-        <v>18400</v>
-      </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>16600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>11600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>25600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>13900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>9200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>3700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>18200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>5400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>37100</v>
-      </c>
-      <c r="R42" s="3">
-        <v>2300</v>
-      </c>
-      <c r="S42" s="3">
-        <v>3200</v>
       </c>
       <c r="T42" s="3">
         <v>2300</v>
       </c>
       <c r="U42" s="3">
+        <v>3200</v>
+      </c>
+      <c r="V42" s="3">
+        <v>2300</v>
+      </c>
+      <c r="W42" s="3">
         <v>3500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>1300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>1100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>11000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>13000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>33700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>3500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>2000</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD42" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3437,8 +3621,14 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3523,8 +3713,14 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3609,8 +3805,14 @@
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3695,8 +3897,14 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3781,117 +3989,129 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
+      <c r="D48" s="3">
+        <v>6400</v>
       </c>
       <c r="E48" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F48" s="3">
+        <v>7300</v>
+      </c>
+      <c r="G48" s="3">
         <v>6600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>6700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J48" s="3">
         <v>5900</v>
-      </c>
-      <c r="H48" s="3">
-        <v>5600</v>
-      </c>
-      <c r="I48" s="3">
-        <v>5500</v>
-      </c>
-      <c r="J48" s="3">
-        <v>5500</v>
       </c>
       <c r="K48" s="3">
         <v>5500</v>
       </c>
       <c r="L48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="M48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="N48" s="3">
         <v>5600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>5600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>4700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>4700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>4800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>4800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>4900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>5000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>5100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>5100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>5200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>5200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>5300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>7300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>7600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>7700</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
+      <c r="D49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -3953,8 +4173,14 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4265,14 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,8 +4357,14 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4211,8 +4449,14 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,94 +4541,106 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>318000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>327200</v>
+      </c>
+      <c r="F54" s="3">
         <v>332000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>333100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
+        <v>323000</v>
+      </c>
+      <c r="I54" s="3">
         <v>313800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>330400</v>
       </c>
-      <c r="H54" s="3">
-        <v>341700</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>357100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>355300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>352600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>337800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>339000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>285800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>293400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>278000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>292200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>258100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>258300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>259600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>262700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>268300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>265900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>260600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>256500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>270300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>236200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>236100</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4671,10 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,94 +4705,102 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>5</v>
+      <c r="D57" s="3">
+        <v>200</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3">
+        <v>200</v>
+      </c>
+      <c r="M57" s="3">
+        <v>200</v>
+      </c>
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>400</v>
+      </c>
+      <c r="R57" s="3">
+        <v>300</v>
+      </c>
+      <c r="S57" s="3">
+        <v>100</v>
+      </c>
+      <c r="T57" s="3">
+        <v>800</v>
+      </c>
+      <c r="U57" s="3">
+        <v>600</v>
+      </c>
+      <c r="V57" s="3">
+        <v>400</v>
+      </c>
+      <c r="W57" s="3">
+        <v>100</v>
+      </c>
+      <c r="X57" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
-        <v>100</v>
-      </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
-        <v>400</v>
-      </c>
-      <c r="O57" s="3">
-        <v>400</v>
-      </c>
-      <c r="P57" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>100</v>
-      </c>
-      <c r="R57" s="3">
-        <v>800</v>
-      </c>
-      <c r="S57" s="3">
-        <v>600</v>
-      </c>
-      <c r="T57" s="3">
-        <v>400</v>
-      </c>
-      <c r="U57" s="3">
-        <v>100</v>
-      </c>
-      <c r="V57" s="3">
-        <v>500</v>
-      </c>
-      <c r="W57" s="3">
-        <v>400</v>
-      </c>
-      <c r="X57" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>500</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>300</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>200</v>
-      </c>
-      <c r="AC57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4619,8 +4885,14 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4705,8 +4977,14 @@
       <c r="AD59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4791,8 +5069,14 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4877,8 +5161,14 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4963,8 +5253,14 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5345,14 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5437,14 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,94 +5529,106 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>5</v>
+      <c r="D66" s="3">
+        <v>243800</v>
       </c>
       <c r="E66" s="3">
+        <v>253400</v>
+      </c>
+      <c r="F66" s="3">
+        <v>256700</v>
+      </c>
+      <c r="G66" s="3">
         <v>257500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
+        <v>244900</v>
+      </c>
+      <c r="I66" s="3">
         <v>236300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>246600</v>
       </c>
-      <c r="H66" s="3">
-        <v>254500</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>263100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>259500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>255800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>238700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>235700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>183100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>191400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>177000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>230300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>196800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>197100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>198700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>202400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>208800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>206600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>201600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>197000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>235900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>201800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>202000</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5659,10 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5747,14 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5839,14 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5931,14 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,94 +6023,106 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>5</v>
+      <c r="D72" s="3">
+        <v>43800</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="3">
+        <v>42700</v>
+      </c>
+      <c r="I72" s="3">
         <v>42100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>41600</v>
       </c>
-      <c r="H72" s="3">
-        <v>40900</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>40400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>40000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>39500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>39100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>38400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>37900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>37300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>37000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>36600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>36000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>35600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>35200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>35000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>34800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>34400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>34100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>33900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>34400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>34300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>34200</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6207,14 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6299,14 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,94 +6391,106 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>74300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>73700</v>
+      </c>
+      <c r="F76" s="3">
         <v>75400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>75500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
+        <v>78100</v>
+      </c>
+      <c r="I76" s="3">
         <v>77500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>83900</v>
       </c>
-      <c r="H76" s="3">
-        <v>87200</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>94000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>95800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>96800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>99100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>103300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>102600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>102000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>101000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>61900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>61300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>61200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>60800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>60400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>59500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>59300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>59000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>59500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>34400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>34300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>34200</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6575,203 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>5</v>
+      <c r="D81" s="3">
+        <v>1500</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3">
         <v>500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>600</v>
       </c>
       <c r="H81" s="3">
         <v>600</v>
       </c>
       <c r="I81" s="3">
+        <v>500</v>
+      </c>
+      <c r="J81" s="3">
+        <v>600</v>
+      </c>
+      <c r="K81" s="3">
         <v>400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>500</v>
-      </c>
-      <c r="K81" s="3">
-        <v>500</v>
-      </c>
-      <c r="L81" s="3">
-        <v>700</v>
       </c>
       <c r="M81" s="3">
         <v>500</v>
       </c>
       <c r="N81" s="3">
+        <v>700</v>
+      </c>
+      <c r="O81" s="3">
         <v>500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q81" s="3">
         <v>800</v>
-      </c>
-      <c r="P81" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>500</v>
       </c>
       <c r="R81" s="3">
         <v>400</v>
       </c>
       <c r="S81" s="3">
+        <v>500</v>
+      </c>
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
+        <v>400</v>
+      </c>
+      <c r="V81" s="3">
         <v>200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-400</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="3">
         <v>100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-300</v>
       </c>
-      <c r="AD81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,8 +6802,10 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6419,26 +6815,26 @@
       <c r="E83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="3">
-        <v>200</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>-200</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
@@ -6447,13 +6843,13 @@
         <v>100</v>
       </c>
       <c r="O83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R83" s="3">
         <v>100</v>
@@ -6494,8 +6890,14 @@
       <c r="AD83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6982,14 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +7074,14 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +7166,14 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7258,14 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,8 +7350,14 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6935,83 +7367,89 @@
       <c r="E89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F89" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I89" s="3">
         <v>900</v>
       </c>
-      <c r="H89" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
+        <v>900</v>
+      </c>
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>4600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>2000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,26 +7480,28 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -7087,14 +7527,14 @@
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -7111,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -7120,16 +7560,22 @@
         <v>-100</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7660,14 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,8 +7752,14 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7311,83 +7769,89 @@
       <c r="E94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F94" s="3">
-        <v>-12900</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="J94" s="3">
         <v>-2300</v>
       </c>
-      <c r="H94" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-14400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>19100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>9600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>17000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>38400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-5200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-19300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>6200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>6700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-12700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>3100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7882,10 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7504,8 +7970,14 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +8062,14 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +8154,14 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,8 +8246,14 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7773,83 +8263,89 @@
       <c r="E100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F100" s="3">
-        <v>-41200</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3">
+        <v>6800</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="J100" s="3">
         <v>-11000</v>
       </c>
-      <c r="H100" s="3">
-        <v>-30900</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>14900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>14000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-4000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-8000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-15800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>34100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-3600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-4200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-6100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>1900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>4900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>4600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-12600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>33600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7934,8 +8430,14 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7945,79 +8447,85 @@
       <c r="E102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F102" s="3">
-        <v>-51000</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="F102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="J102" s="3">
         <v>-12400</v>
       </c>
-      <c r="H102" s="3">
-        <v>-37800</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-13100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>38600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>25300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>17600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>34000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-12200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-19800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>35200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>2800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>1600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-6800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-20400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>26400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-2200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FFBW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FFBW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
   <si>
     <t>FFBW</t>
   </si>
@@ -656,195 +656,203 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F8" s="3">
         <v>15500</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3">
         <v>3600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>3200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2700</v>
-      </c>
-      <c r="M8" s="3">
-        <v>2800</v>
-      </c>
-      <c r="N8" s="3">
-        <v>3200</v>
       </c>
       <c r="O8" s="3">
         <v>2800</v>
       </c>
       <c r="P8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="R8" s="3">
         <v>2700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>5600</v>
-      </c>
-      <c r="R8" s="3">
-        <v>2800</v>
-      </c>
-      <c r="S8" s="3">
-        <v>2900</v>
       </c>
       <c r="T8" s="3">
         <v>2800</v>
       </c>
       <c r="U8" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="V8" s="3">
         <v>2800</v>
@@ -853,34 +861,40 @@
         <v>2800</v>
       </c>
       <c r="X8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Z8" s="3">
         <v>2700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>2700</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>2300</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>2400</v>
       </c>
       <c r="AB8" s="3">
         <v>2300</v>
       </c>
       <c r="AC8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AE8" s="3">
         <v>2200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>2100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -971,8 +985,14 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1063,8 +1083,14 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1097,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1189,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1281,8 +1315,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1373,8 +1413,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1465,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1496,79 +1548,81 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F17" s="3">
         <v>4700</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3">
         <v>800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>300</v>
-      </c>
-      <c r="J17" s="3">
-        <v>200</v>
-      </c>
-      <c r="K17" s="3">
-        <v>200</v>
       </c>
       <c r="L17" s="3">
         <v>200</v>
       </c>
       <c r="M17" s="3">
+        <v>200</v>
+      </c>
+      <c r="N17" s="3">
+        <v>200</v>
+      </c>
+      <c r="O17" s="3">
         <v>300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>700</v>
-      </c>
-      <c r="T17" s="3">
-        <v>800</v>
-      </c>
-      <c r="U17" s="3">
-        <v>800</v>
       </c>
       <c r="V17" s="3">
         <v>800</v>
       </c>
       <c r="W17" s="3">
+        <v>800</v>
+      </c>
+      <c r="X17" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y17" s="3">
         <v>700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>700</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>600</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>500</v>
       </c>
       <c r="AA17" s="3">
         <v>600</v>
@@ -1577,81 +1631,87 @@
         <v>500</v>
       </c>
       <c r="AC17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE17" s="3">
         <v>400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F18" s="3">
         <v>10800</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3">
         <v>2800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>3000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>2900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>2800</v>
-      </c>
-      <c r="K18" s="3">
-        <v>2500</v>
-      </c>
-      <c r="L18" s="3">
-        <v>2500</v>
       </c>
       <c r="M18" s="3">
         <v>2500</v>
       </c>
       <c r="N18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="P18" s="3">
         <v>2900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>2300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>4400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>2200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>2200</v>
-      </c>
-      <c r="T18" s="3">
-        <v>2000</v>
-      </c>
-      <c r="U18" s="3">
-        <v>2000</v>
       </c>
       <c r="V18" s="3">
         <v>2000</v>
       </c>
       <c r="W18" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="X18" s="3">
         <v>2000</v>
@@ -1660,10 +1720,10 @@
         <v>2100</v>
       </c>
       <c r="Z18" s="3">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="AA18" s="3">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="AB18" s="3">
         <v>1800</v>
@@ -1672,16 +1732,22 @@
         <v>1800</v>
       </c>
       <c r="AD18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AF18" s="3">
         <v>1700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>1200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1714,100 +1780,108 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F20" s="3">
         <v>-8400</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-2100</v>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I20" s="3">
         <v>-2200</v>
       </c>
       <c r="J20" s="3">
-        <v>-1900</v>
+        <v>-2100</v>
       </c>
       <c r="K20" s="3">
-        <v>-1800</v>
+        <v>-2200</v>
       </c>
       <c r="L20" s="3">
         <v>-1900</v>
       </c>
       <c r="M20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="O20" s="3">
         <v>-2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-3300</v>
       </c>
       <c r="R20" s="3">
         <v>-1700</v>
       </c>
       <c r="S20" s="3">
-        <v>-1500</v>
+        <v>-3300</v>
       </c>
       <c r="T20" s="3">
-        <v>-1500</v>
+        <v>-1700</v>
       </c>
       <c r="U20" s="3">
         <v>-1500</v>
       </c>
       <c r="V20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="W20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-1800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1823,83 +1897,89 @@
       <c r="G21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K21" s="3">
+        <v>800</v>
+      </c>
+      <c r="L21" s="3">
         <v>900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="M21" s="3">
+        <v>700</v>
+      </c>
+      <c r="N21" s="3">
         <v>800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="O21" s="3">
+        <v>600</v>
+      </c>
+      <c r="P21" s="3">
         <v>900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="Q21" s="3">
+        <v>800</v>
+      </c>
+      <c r="R21" s="3">
         <v>700</v>
       </c>
-      <c r="L21" s="3">
-        <v>800</v>
-      </c>
-      <c r="M21" s="3">
-        <v>600</v>
-      </c>
-      <c r="N21" s="3">
-        <v>900</v>
-      </c>
-      <c r="O21" s="3">
-        <v>800</v>
-      </c>
-      <c r="P21" s="3">
-        <v>700</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1200</v>
-      </c>
-      <c r="R21" s="3">
-        <v>600</v>
-      </c>
-      <c r="S21" s="3">
-        <v>800</v>
       </c>
       <c r="T21" s="3">
         <v>600</v>
       </c>
       <c r="U21" s="3">
+        <v>800</v>
+      </c>
+      <c r="V21" s="3">
         <v>600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
+        <v>600</v>
+      </c>
+      <c r="X21" s="3">
         <v>400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-400</v>
       </c>
-      <c r="AF21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1990,114 +2070,126 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2400</v>
+        <v>800</v>
       </c>
       <c r="E23" s="3">
         <v>600</v>
       </c>
       <c r="F23" s="3">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="G23" s="3">
         <v>600</v>
       </c>
       <c r="H23" s="3">
+        <v>600</v>
+      </c>
+      <c r="I23" s="3">
+        <v>600</v>
+      </c>
+      <c r="J23" s="3">
         <v>800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>900</v>
-      </c>
-      <c r="K23" s="3">
-        <v>600</v>
-      </c>
-      <c r="L23" s="3">
-        <v>600</v>
       </c>
       <c r="M23" s="3">
         <v>600</v>
       </c>
       <c r="N23" s="3">
+        <v>600</v>
+      </c>
+      <c r="O23" s="3">
+        <v>600</v>
+      </c>
+      <c r="P23" s="3">
         <v>900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1100</v>
-      </c>
-      <c r="R23" s="3">
-        <v>500</v>
-      </c>
-      <c r="S23" s="3">
-        <v>700</v>
       </c>
       <c r="T23" s="3">
         <v>500</v>
       </c>
       <c r="U23" s="3">
+        <v>700</v>
+      </c>
+      <c r="V23" s="3">
         <v>500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
+        <v>500</v>
+      </c>
+      <c r="X23" s="3">
         <v>300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-200</v>
       </c>
-      <c r="AB23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="3">
         <v>100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="G24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H24" s="3">
         <v>200</v>
@@ -2112,19 +2204,19 @@
         <v>200</v>
       </c>
       <c r="L24" s="3">
+        <v>200</v>
+      </c>
+      <c r="M24" s="3">
+        <v>200</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
-      </c>
-      <c r="O24" s="3">
-        <v>200</v>
-      </c>
-      <c r="P24" s="3">
-        <v>100</v>
       </c>
       <c r="Q24" s="3">
         <v>200</v>
@@ -2139,7 +2231,7 @@
         <v>100</v>
       </c>
       <c r="U24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V24" s="3">
         <v>100</v>
@@ -2157,25 +2249,31 @@
         <v>100</v>
       </c>
       <c r="AA24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-100</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>-200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2266,25 +2364,31 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>500</v>
+      </c>
+      <c r="F26" s="3">
         <v>1500</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G26" s="3">
-        <v>500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>600</v>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I26" s="3">
         <v>500</v>
@@ -2293,90 +2397,96 @@
         <v>600</v>
       </c>
       <c r="K26" s="3">
+        <v>500</v>
+      </c>
+      <c r="L26" s="3">
+        <v>600</v>
+      </c>
+      <c r="M26" s="3">
         <v>400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>500</v>
-      </c>
-      <c r="M26" s="3">
-        <v>500</v>
-      </c>
-      <c r="N26" s="3">
-        <v>700</v>
       </c>
       <c r="O26" s="3">
         <v>500</v>
       </c>
       <c r="P26" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q26" s="3">
         <v>500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
+        <v>500</v>
+      </c>
+      <c r="S26" s="3">
         <v>800</v>
-      </c>
-      <c r="R26" s="3">
-        <v>400</v>
-      </c>
-      <c r="S26" s="3">
-        <v>500</v>
       </c>
       <c r="T26" s="3">
         <v>400</v>
       </c>
       <c r="U26" s="3">
+        <v>500</v>
+      </c>
+      <c r="V26" s="3">
         <v>400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
+        <v>400</v>
+      </c>
+      <c r="X26" s="3">
         <v>200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-100</v>
       </c>
-      <c r="AB26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="3">
         <v>100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-300</v>
       </c>
-      <c r="AF26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>500</v>
+      </c>
+      <c r="F27" s="3">
         <v>1500</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="3">
-        <v>500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>600</v>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I27" s="3">
         <v>500</v>
@@ -2385,73 +2495,79 @@
         <v>600</v>
       </c>
       <c r="K27" s="3">
+        <v>500</v>
+      </c>
+      <c r="L27" s="3">
+        <v>600</v>
+      </c>
+      <c r="M27" s="3">
         <v>400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
-      </c>
-      <c r="M27" s="3">
-        <v>500</v>
-      </c>
-      <c r="N27" s="3">
-        <v>700</v>
       </c>
       <c r="O27" s="3">
         <v>500</v>
       </c>
       <c r="P27" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q27" s="3">
         <v>500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
+        <v>500</v>
+      </c>
+      <c r="S27" s="3">
         <v>800</v>
-      </c>
-      <c r="R27" s="3">
-        <v>400</v>
-      </c>
-      <c r="S27" s="3">
-        <v>500</v>
       </c>
       <c r="T27" s="3">
         <v>400</v>
       </c>
       <c r="U27" s="3">
+        <v>500</v>
+      </c>
+      <c r="V27" s="3">
         <v>400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
+        <v>400</v>
+      </c>
+      <c r="X27" s="3">
         <v>200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-100</v>
       </c>
-      <c r="AB27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="3">
         <v>100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-300</v>
       </c>
-      <c r="AF27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2542,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2598,33 +2720,33 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-400</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2634,8 +2756,14 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2726,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2818,117 +2952,129 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F32" s="3">
         <v>8400</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2100</v>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I32" s="3">
         <v>2200</v>
       </c>
       <c r="J32" s="3">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="K32" s="3">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="L32" s="3">
         <v>1900</v>
       </c>
       <c r="M32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O32" s="3">
         <v>2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>1600</v>
-      </c>
-      <c r="P32" s="3">
-        <v>1700</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>3300</v>
       </c>
       <c r="R32" s="3">
         <v>1700</v>
       </c>
       <c r="S32" s="3">
-        <v>1500</v>
+        <v>3300</v>
       </c>
       <c r="T32" s="3">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="U32" s="3">
         <v>1500</v>
       </c>
       <c r="V32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X32" s="3">
         <v>1700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>1800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>1500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>1600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>1600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>1900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>1800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>1600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>1600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>1700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>500</v>
+      </c>
+      <c r="F33" s="3">
         <v>1500</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="3">
-        <v>500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>600</v>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I33" s="3">
         <v>500</v>
@@ -2937,73 +3083,79 @@
         <v>600</v>
       </c>
       <c r="K33" s="3">
+        <v>500</v>
+      </c>
+      <c r="L33" s="3">
+        <v>600</v>
+      </c>
+      <c r="M33" s="3">
         <v>400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
-      </c>
-      <c r="M33" s="3">
-        <v>500</v>
-      </c>
-      <c r="N33" s="3">
-        <v>700</v>
       </c>
       <c r="O33" s="3">
         <v>500</v>
       </c>
       <c r="P33" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q33" s="3">
         <v>500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
+        <v>500</v>
+      </c>
+      <c r="S33" s="3">
         <v>800</v>
-      </c>
-      <c r="R33" s="3">
-        <v>400</v>
-      </c>
-      <c r="S33" s="3">
-        <v>500</v>
       </c>
       <c r="T33" s="3">
         <v>400</v>
       </c>
       <c r="U33" s="3">
+        <v>500</v>
+      </c>
+      <c r="V33" s="3">
         <v>400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
+        <v>400</v>
+      </c>
+      <c r="X33" s="3">
         <v>200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-400</v>
       </c>
-      <c r="AB33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="3">
         <v>100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-300</v>
       </c>
-      <c r="AF33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3094,25 +3246,31 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>500</v>
+      </c>
+      <c r="F35" s="3">
         <v>1500</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="3">
-        <v>500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>600</v>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I35" s="3">
         <v>500</v>
@@ -3121,170 +3279,182 @@
         <v>600</v>
       </c>
       <c r="K35" s="3">
+        <v>500</v>
+      </c>
+      <c r="L35" s="3">
+        <v>600</v>
+      </c>
+      <c r="M35" s="3">
         <v>400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
-      </c>
-      <c r="M35" s="3">
-        <v>500</v>
-      </c>
-      <c r="N35" s="3">
-        <v>700</v>
       </c>
       <c r="O35" s="3">
         <v>500</v>
       </c>
       <c r="P35" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q35" s="3">
         <v>500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
+        <v>500</v>
+      </c>
+      <c r="S35" s="3">
         <v>800</v>
-      </c>
-      <c r="R35" s="3">
-        <v>400</v>
-      </c>
-      <c r="S35" s="3">
-        <v>500</v>
       </c>
       <c r="T35" s="3">
         <v>400</v>
       </c>
       <c r="U35" s="3">
+        <v>500</v>
+      </c>
+      <c r="V35" s="3">
         <v>400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
+        <v>400</v>
+      </c>
+      <c r="X35" s="3">
         <v>200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-400</v>
       </c>
-      <c r="AB35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="3">
         <v>100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-300</v>
       </c>
-      <c r="AF35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3317,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3351,192 +3523,206 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F41" s="3">
         <v>5800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>7800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>11400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>10900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>15700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>30900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>52500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>71000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>62000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>50700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>41500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>5300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>11000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>4100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>4200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>3400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>3300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>5800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>5000</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" s="3">
         <v>1800</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H42" s="3">
+      <c r="H42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J42" s="3">
         <v>2000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>2300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>13400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>16600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>11600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>25600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>13900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>9200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>3700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>18200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>5400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>37100</v>
-      </c>
-      <c r="T42" s="3">
-        <v>2300</v>
-      </c>
-      <c r="U42" s="3">
-        <v>3200</v>
       </c>
       <c r="V42" s="3">
         <v>2300</v>
       </c>
       <c r="W42" s="3">
+        <v>3200</v>
+      </c>
+      <c r="X42" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Y42" s="3">
         <v>3500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>1300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>1100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>11000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>13000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>33700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>3500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>2000</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF42" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3627,8 +3813,14 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3719,8 +3911,14 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3811,8 +4009,14 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3903,8 +4107,14 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3995,129 +4205,141 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E48" s="3">
         <v>6400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="G48" s="3">
         <v>7200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>7300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>6600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>6700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>6700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>5900</v>
-      </c>
-      <c r="K48" s="3">
-        <v>5500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>5500</v>
       </c>
       <c r="M48" s="3">
         <v>5500</v>
       </c>
       <c r="N48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="O48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="P48" s="3">
         <v>5600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>5600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>4600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>4700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>4700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>4800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>4800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>4900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>5000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>5100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>5100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>5200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>5200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>5300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>7300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>7600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>7700</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>5</v>
+      <c r="D49" s="3">
+        <v>100</v>
       </c>
       <c r="E49" s="3">
-        <v>200</v>
-      </c>
-      <c r="F49" s="3">
-        <v>200</v>
+        <v>100</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G49" s="3">
         <v>200</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
+      <c r="H49" s="3">
+        <v>200</v>
+      </c>
+      <c r="I49" s="3">
+        <v>200</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -4179,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4271,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4363,8 +4597,14 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4455,8 +4695,14 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4547,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>308000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>326300</v>
+      </c>
+      <c r="F54" s="3">
         <v>318000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>327200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>332000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>333100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>323000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>313800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>330400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>357100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>355300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>352600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>337800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>339000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>285800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>293400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>278000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>292200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>258100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>258300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>259600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>262700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>268300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>265900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>260600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>256500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>270300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>236200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>236100</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4673,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4707,100 +4967,108 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
         <v>400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>200</v>
       </c>
-      <c r="AA57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="3">
         <v>500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>200</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4891,8 +5159,14 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4983,8 +5257,14 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5075,8 +5355,14 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5167,8 +5453,14 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5259,8 +5551,14 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5351,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5443,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5535,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>233700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>252200</v>
+      </c>
+      <c r="F66" s="3">
         <v>243800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>253400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>256700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>257500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>244900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>236300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>246600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>263100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>259500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>255800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>238700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>235700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>183100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>191400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>177000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>230300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>196800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>197100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>198700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>202400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>208800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>206600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>201600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>197000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>235900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>201800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>202000</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5661,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5753,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5845,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5937,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6029,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3">
         <v>43800</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3">
         <v>42700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>42100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>41600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>40400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>40000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>39500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>39100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>38400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>37900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>37300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>37000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>36600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>36000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>35600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>35200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>35000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>34800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>34400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>34100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>33900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>34400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>34300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>34200</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6213,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6305,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6397,8 +6763,14 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6406,91 +6778,97 @@
         <v>74300</v>
       </c>
       <c r="E76" s="3">
+        <v>74100</v>
+      </c>
+      <c r="F76" s="3">
+        <v>74300</v>
+      </c>
+      <c r="G76" s="3">
         <v>73700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>75400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>75500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>78100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>77500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>83900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>94000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>95800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>96800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>99100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>103300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>102600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>102000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>101000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>61900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>61300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>61200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>60800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>60400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>59500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>59300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>59000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>59500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>34400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>34300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>34200</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6581,122 +6959,134 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>500</v>
+      </c>
+      <c r="F81" s="3">
         <v>1500</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G81" s="3">
-        <v>500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>600</v>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I81" s="3">
         <v>500</v>
@@ -6705,73 +7095,79 @@
         <v>600</v>
       </c>
       <c r="K81" s="3">
+        <v>500</v>
+      </c>
+      <c r="L81" s="3">
+        <v>600</v>
+      </c>
+      <c r="M81" s="3">
         <v>400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
-      </c>
-      <c r="M81" s="3">
-        <v>500</v>
-      </c>
-      <c r="N81" s="3">
-        <v>700</v>
       </c>
       <c r="O81" s="3">
         <v>500</v>
       </c>
       <c r="P81" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q81" s="3">
         <v>500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
+        <v>500</v>
+      </c>
+      <c r="S81" s="3">
         <v>800</v>
-      </c>
-      <c r="R81" s="3">
-        <v>400</v>
-      </c>
-      <c r="S81" s="3">
-        <v>500</v>
       </c>
       <c r="T81" s="3">
         <v>400</v>
       </c>
       <c r="U81" s="3">
+        <v>500</v>
+      </c>
+      <c r="V81" s="3">
         <v>400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
+        <v>400</v>
+      </c>
+      <c r="X81" s="3">
         <v>200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-400</v>
       </c>
-      <c r="AB81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="3">
         <v>100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-300</v>
       </c>
-      <c r="AF81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6804,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6821,11 +7219,11 @@
       <c r="G83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H83" s="3">
-        <v>100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>100</v>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -6834,13 +7232,13 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
@@ -6849,13 +7247,13 @@
         <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>100</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T83" s="3">
         <v>100</v>
@@ -6896,8 +7294,14 @@
       <c r="AF83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6988,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7080,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7172,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7264,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7356,8 +7784,14 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7373,83 +7807,89 @@
       <c r="G89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3">
         <v>1300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>4600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>2000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>1900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7482,8 +7922,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7533,14 +7975,14 @@
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
@@ -7557,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -7566,16 +8008,22 @@
         <v>-100</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7666,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7758,8 +8212,14 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7775,83 +8235,89 @@
       <c r="G94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3">
         <v>-13300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-11400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-14400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>19100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>9600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>17000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>38400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-19300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-9800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-1400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>6200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>6700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>3100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7884,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7976,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8068,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8160,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8252,8 +8738,14 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8269,83 +8761,89 @@
       <c r="G100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3">
         <v>6800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-15800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-11000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>1600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>14900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>14000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-4000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-15800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>34100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-3600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-4200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-6100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>1900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>4900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>4600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-12600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>33600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8436,8 +8934,14 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8453,79 +8957,85 @@
       <c r="G102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H102" s="3">
+      <c r="H102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3">
         <v>-5200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-26300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-12400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-13100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>38600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>25300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>17600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>34000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-19800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-24500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>35200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>2800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-20400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>26400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-2200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FFBW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FFBW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
   <si>
     <t>FFBW</t>
   </si>
@@ -656,206 +656,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4200</v>
+        <v>3100</v>
       </c>
       <c r="E8" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="F8" s="3">
-        <v>15500</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>5</v>
+        <v>2900</v>
+      </c>
+      <c r="G8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2900</v>
       </c>
       <c r="I8" s="3">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="J8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K8" s="3">
         <v>3400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3000</v>
-      </c>
-      <c r="M8" s="3">
-        <v>2700</v>
       </c>
       <c r="N8" s="3">
         <v>2700</v>
       </c>
       <c r="O8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="P8" s="3">
         <v>2800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2900</v>
-      </c>
-      <c r="V8" s="3">
-        <v>2800</v>
       </c>
       <c r="W8" s="3">
         <v>2800</v>
@@ -867,34 +871,37 @@
         <v>2800</v>
       </c>
       <c r="Z8" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="AA8" s="3">
         <v>2700</v>
       </c>
       <c r="AB8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AC8" s="3">
         <v>2300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2200</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>2100</v>
       </c>
       <c r="AG8" s="3">
         <v>2100</v>
       </c>
       <c r="AH8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AI8" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,31 +998,34 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,31 +1338,34 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1419,31 +1439,34 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,37 +1576,38 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1400</v>
+        <v>2200</v>
       </c>
       <c r="E17" s="3">
-        <v>1400</v>
+        <v>2200</v>
       </c>
       <c r="F17" s="3">
-        <v>4700</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>5</v>
+        <v>2200</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H17" s="3">
+        <v>2400</v>
       </c>
       <c r="I17" s="3">
-        <v>800</v>
+        <v>2300</v>
       </c>
       <c r="J17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K17" s="3">
         <v>400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>300</v>
-      </c>
-      <c r="L17" s="3">
-        <v>200</v>
       </c>
       <c r="M17" s="3">
         <v>200</v>
@@ -1589,28 +1616,28 @@
         <v>200</v>
       </c>
       <c r="O17" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P17" s="3">
         <v>300</v>
       </c>
       <c r="Q17" s="3">
+        <v>300</v>
+      </c>
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>700</v>
-      </c>
-      <c r="V17" s="3">
-        <v>800</v>
       </c>
       <c r="W17" s="3">
         <v>800</v>
@@ -1619,69 +1646,72 @@
         <v>800</v>
       </c>
       <c r="Y17" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="Z17" s="3">
         <v>700</v>
       </c>
       <c r="AA17" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB17" s="3">
         <v>600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>500</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>400</v>
       </c>
       <c r="AF17" s="3">
         <v>400</v>
       </c>
       <c r="AG17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH17" s="3">
         <v>900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>800</v>
+      </c>
+      <c r="F18" s="3">
+        <v>600</v>
+      </c>
+      <c r="G18" s="3">
+        <v>600</v>
+      </c>
+      <c r="H18" s="3">
+        <v>600</v>
+      </c>
+      <c r="I18" s="3">
+        <v>600</v>
+      </c>
+      <c r="J18" s="3">
+        <v>600</v>
+      </c>
+      <c r="K18" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>2900</v>
+      </c>
+      <c r="M18" s="3">
         <v>2800</v>
-      </c>
-      <c r="E18" s="3">
-        <v>2600</v>
-      </c>
-      <c r="F18" s="3">
-        <v>10800</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I18" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J18" s="3">
-        <v>3000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>2900</v>
-      </c>
-      <c r="L18" s="3">
-        <v>2800</v>
-      </c>
-      <c r="M18" s="3">
-        <v>2500</v>
       </c>
       <c r="N18" s="3">
         <v>2500</v>
@@ -1690,25 +1720,25 @@
         <v>2500</v>
       </c>
       <c r="P18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Q18" s="3">
         <v>2900</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>2300</v>
       </c>
       <c r="R18" s="3">
         <v>2300</v>
       </c>
       <c r="S18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="T18" s="3">
         <v>4400</v>
-      </c>
-      <c r="T18" s="3">
-        <v>2200</v>
       </c>
       <c r="U18" s="3">
         <v>2200</v>
       </c>
       <c r="V18" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="W18" s="3">
         <v>2000</v>
@@ -1717,16 +1747,16 @@
         <v>2000</v>
       </c>
       <c r="Y18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z18" s="3">
         <v>2100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2100</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>1800</v>
       </c>
       <c r="AC18" s="3">
         <v>1800</v>
@@ -1738,16 +1768,19 @@
         <v>1800</v>
       </c>
       <c r="AF18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AG18" s="3">
         <v>1700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,64 +1815,65 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="P20" s="3">
         <v>-2000</v>
       </c>
-      <c r="E20" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="Q20" s="3">
         <v>-2100</v>
       </c>
-      <c r="K20" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1700</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-1500</v>
       </c>
       <c r="V20" s="3">
         <v>-1500</v>
@@ -1848,161 +1882,167 @@
         <v>-1500</v>
       </c>
       <c r="X20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-1600</v>
       </c>
       <c r="AB20" s="3">
         <v>-1600</v>
       </c>
       <c r="AC20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-1600</v>
       </c>
       <c r="AF20" s="3">
         <v>-1600</v>
       </c>
       <c r="AG20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="D21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>900</v>
+      </c>
+      <c r="F21" s="3">
+        <v>700</v>
+      </c>
+      <c r="G21" s="3">
+        <v>700</v>
+      </c>
+      <c r="H21" s="3">
+        <v>600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>700</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="3">
         <v>800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>800</v>
-      </c>
-      <c r="V21" s="3">
-        <v>600</v>
       </c>
       <c r="W21" s="3">
         <v>600</v>
       </c>
       <c r="X21" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="Y21" s="3">
         <v>400</v>
       </c>
       <c r="Z21" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AA21" s="3">
         <v>500</v>
       </c>
       <c r="AB21" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC21" s="3">
         <v>300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-400</v>
       </c>
-      <c r="AH21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2076,19 +2116,22 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>900</v>
+      </c>
+      <c r="E23" s="3">
         <v>800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>600</v>
-      </c>
-      <c r="F23" s="3">
-        <v>2400</v>
       </c>
       <c r="G23" s="3">
         <v>600</v>
@@ -2100,16 +2143,16 @@
         <v>600</v>
       </c>
       <c r="J23" s="3">
+        <v>600</v>
+      </c>
+      <c r="K23" s="3">
         <v>800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>900</v>
-      </c>
-      <c r="M23" s="3">
-        <v>600</v>
       </c>
       <c r="N23" s="3">
         <v>600</v>
@@ -2118,81 +2161,84 @@
         <v>600</v>
       </c>
       <c r="P23" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q23" s="3">
         <v>900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>700</v>
-      </c>
-      <c r="V23" s="3">
-        <v>500</v>
       </c>
       <c r="W23" s="3">
         <v>500</v>
       </c>
       <c r="X23" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="Y23" s="3">
         <v>300</v>
       </c>
       <c r="Z23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA23" s="3">
         <v>500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-200</v>
       </c>
-      <c r="AD23" s="3">
-        <v>0</v>
-      </c>
       <c r="AE23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF23" s="3">
         <v>100</v>
       </c>
       <c r="AG23" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH23" s="3">
         <v>-500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3">
+        <v>400</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>200</v>
       </c>
       <c r="I24" s="3">
         <v>200</v>
@@ -2210,31 +2256,31 @@
         <v>200</v>
       </c>
       <c r="N24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O24" s="3">
         <v>100</v>
       </c>
       <c r="P24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="3">
         <v>200</v>
       </c>
       <c r="R24" s="3">
+        <v>200</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
-      </c>
-      <c r="V24" s="3">
-        <v>100</v>
       </c>
       <c r="W24" s="3">
         <v>100</v>
@@ -2255,11 +2301,11 @@
         <v>100</v>
       </c>
       <c r="AC24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-100</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
         <v>0</v>
       </c>
@@ -2267,13 +2313,16 @@
         <v>0</v>
       </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>-200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>700</v>
+      </c>
+      <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>500</v>
       </c>
-      <c r="F26" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>5</v>
+      <c r="G26" s="3">
+        <v>100</v>
+      </c>
+      <c r="H26" s="3">
+        <v>400</v>
       </c>
       <c r="I26" s="3">
         <v>500</v>
       </c>
       <c r="J26" s="3">
+        <v>500</v>
+      </c>
+      <c r="K26" s="3">
         <v>600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>400</v>
-      </c>
-      <c r="N26" s="3">
-        <v>500</v>
       </c>
       <c r="O26" s="3">
         <v>500</v>
       </c>
       <c r="P26" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q26" s="3">
         <v>700</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>500</v>
       </c>
       <c r="R26" s="3">
         <v>500</v>
       </c>
       <c r="S26" s="3">
+        <v>500</v>
+      </c>
+      <c r="T26" s="3">
         <v>800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>500</v>
-      </c>
-      <c r="V26" s="3">
-        <v>400</v>
       </c>
       <c r="W26" s="3">
         <v>400</v>
       </c>
       <c r="X26" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Y26" s="3">
         <v>200</v>
       </c>
       <c r="Z26" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA26" s="3">
         <v>300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-100</v>
       </c>
-      <c r="AD26" s="3">
-        <v>0</v>
-      </c>
       <c r="AE26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF26" s="3">
         <v>100</v>
       </c>
       <c r="AG26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH26" s="3">
         <v>-300</v>
       </c>
-      <c r="AH26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>700</v>
+      </c>
+      <c r="E27" s="3">
         <v>600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>500</v>
       </c>
-      <c r="F27" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>5</v>
+      <c r="G27" s="3">
+        <v>100</v>
+      </c>
+      <c r="H27" s="3">
+        <v>400</v>
       </c>
       <c r="I27" s="3">
         <v>500</v>
       </c>
       <c r="J27" s="3">
+        <v>500</v>
+      </c>
+      <c r="K27" s="3">
         <v>600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>400</v>
-      </c>
-      <c r="N27" s="3">
-        <v>500</v>
       </c>
       <c r="O27" s="3">
         <v>500</v>
       </c>
       <c r="P27" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q27" s="3">
         <v>700</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>500</v>
       </c>
       <c r="R27" s="3">
         <v>500</v>
       </c>
       <c r="S27" s="3">
+        <v>500</v>
+      </c>
+      <c r="T27" s="3">
         <v>800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>500</v>
-      </c>
-      <c r="V27" s="3">
-        <v>400</v>
       </c>
       <c r="W27" s="3">
         <v>400</v>
       </c>
       <c r="X27" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Y27" s="3">
         <v>200</v>
       </c>
       <c r="Z27" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA27" s="3">
         <v>300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-100</v>
       </c>
-      <c r="AD27" s="3">
-        <v>0</v>
-      </c>
       <c r="AE27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF27" s="3">
         <v>100</v>
       </c>
       <c r="AG27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-300</v>
       </c>
-      <c r="AH27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2726,17 +2787,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -2744,12 +2805,12 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-400</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,64 +3025,67 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P32" s="3">
         <v>2000</v>
       </c>
-      <c r="E32" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F32" s="3">
-        <v>8400</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="Q32" s="3">
         <v>2100</v>
       </c>
-      <c r="K32" s="3">
-        <v>2200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>1900</v>
-      </c>
-      <c r="M32" s="3">
-        <v>1800</v>
-      </c>
-      <c r="N32" s="3">
-        <v>1900</v>
-      </c>
-      <c r="O32" s="3">
-        <v>2000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>2100</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1700</v>
-      </c>
-      <c r="U32" s="3">
-        <v>1500</v>
       </c>
       <c r="V32" s="3">
         <v>1500</v>
@@ -3024,138 +3094,144 @@
         <v>1500</v>
       </c>
       <c r="X32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y32" s="3">
         <v>1700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1500</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>1600</v>
       </c>
       <c r="AB32" s="3">
         <v>1600</v>
       </c>
       <c r="AC32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AD32" s="3">
         <v>1900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1800</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>1600</v>
       </c>
       <c r="AF32" s="3">
         <v>1600</v>
       </c>
       <c r="AG32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AH32" s="3">
         <v>1700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>700</v>
+      </c>
+      <c r="E33" s="3">
         <v>600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>500</v>
       </c>
-      <c r="F33" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>5</v>
+      <c r="G33" s="3">
+        <v>100</v>
+      </c>
+      <c r="H33" s="3">
+        <v>400</v>
       </c>
       <c r="I33" s="3">
         <v>500</v>
       </c>
       <c r="J33" s="3">
+        <v>500</v>
+      </c>
+      <c r="K33" s="3">
         <v>600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>400</v>
-      </c>
-      <c r="N33" s="3">
-        <v>500</v>
       </c>
       <c r="O33" s="3">
         <v>500</v>
       </c>
       <c r="P33" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q33" s="3">
         <v>700</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>500</v>
       </c>
       <c r="R33" s="3">
         <v>500</v>
       </c>
       <c r="S33" s="3">
+        <v>500</v>
+      </c>
+      <c r="T33" s="3">
         <v>800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>500</v>
-      </c>
-      <c r="V33" s="3">
-        <v>400</v>
       </c>
       <c r="W33" s="3">
         <v>400</v>
       </c>
       <c r="X33" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Y33" s="3">
         <v>200</v>
       </c>
       <c r="Z33" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA33" s="3">
         <v>300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-400</v>
       </c>
-      <c r="AD33" s="3">
-        <v>0</v>
-      </c>
       <c r="AE33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF33" s="3">
         <v>100</v>
       </c>
       <c r="AG33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-300</v>
       </c>
-      <c r="AH33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>700</v>
+      </c>
+      <c r="E35" s="3">
         <v>600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>500</v>
       </c>
-      <c r="F35" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>5</v>
+      <c r="G35" s="3">
+        <v>100</v>
+      </c>
+      <c r="H35" s="3">
+        <v>400</v>
       </c>
       <c r="I35" s="3">
         <v>500</v>
       </c>
       <c r="J35" s="3">
+        <v>500</v>
+      </c>
+      <c r="K35" s="3">
         <v>600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>400</v>
-      </c>
-      <c r="N35" s="3">
-        <v>500</v>
       </c>
       <c r="O35" s="3">
         <v>500</v>
       </c>
       <c r="P35" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q35" s="3">
         <v>700</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>500</v>
       </c>
       <c r="R35" s="3">
         <v>500</v>
       </c>
       <c r="S35" s="3">
+        <v>500</v>
+      </c>
+      <c r="T35" s="3">
         <v>800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>500</v>
-      </c>
-      <c r="V35" s="3">
-        <v>400</v>
       </c>
       <c r="W35" s="3">
         <v>400</v>
       </c>
       <c r="X35" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Y35" s="3">
         <v>200</v>
       </c>
       <c r="Z35" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA35" s="3">
         <v>300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-400</v>
       </c>
-      <c r="AD35" s="3">
-        <v>0</v>
-      </c>
       <c r="AE35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF35" s="3">
         <v>100</v>
       </c>
       <c r="AG35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-300</v>
       </c>
-      <c r="AH35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,227 +3611,234 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E41" s="3">
         <v>7600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>52500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>71000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>62000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>50700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>41500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5000</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>5</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>1800</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>200</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>2000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>13400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>16600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>11600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>25600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>13900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>9200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>18200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>5400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>37100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>11000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>13000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>33700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>3500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2000</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3819,31 +3912,34 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3917,31 +4013,34 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+        <v>1000</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4015,31 +4114,34 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>14800</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4113,31 +4215,34 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>37600</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>40100</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>42600</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>40300</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>43700</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>45700</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4211,8 +4316,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4220,31 +4328,31 @@
         <v>6300</v>
       </c>
       <c r="E48" s="3">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="F48" s="3">
         <v>6400</v>
       </c>
       <c r="G48" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H48" s="3">
         <v>7200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6600</v>
-      </c>
-      <c r="J48" s="3">
-        <v>6700</v>
       </c>
       <c r="K48" s="3">
         <v>6700</v>
       </c>
       <c r="L48" s="3">
+        <v>6700</v>
+      </c>
+      <c r="M48" s="3">
         <v>5900</v>
-      </c>
-      <c r="M48" s="3">
-        <v>5500</v>
       </c>
       <c r="N48" s="3">
         <v>5500</v>
@@ -4253,64 +4361,67 @@
         <v>5500</v>
       </c>
       <c r="P48" s="3">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="Q48" s="3">
         <v>5600</v>
       </c>
       <c r="R48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="S48" s="3">
         <v>4600</v>
-      </c>
-      <c r="S48" s="3">
-        <v>4700</v>
       </c>
       <c r="T48" s="3">
         <v>4700</v>
       </c>
       <c r="U48" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="V48" s="3">
         <v>4800</v>
       </c>
       <c r="W48" s="3">
+        <v>4800</v>
+      </c>
+      <c r="X48" s="3">
         <v>4900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5000</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>5100</v>
       </c>
       <c r="Z48" s="3">
         <v>5100</v>
       </c>
       <c r="AA48" s="3">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="AB48" s="3">
         <v>5200</v>
       </c>
       <c r="AC48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AD48" s="3">
         <v>5300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7700</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4320,11 +4431,11 @@
       <c r="E49" s="3">
         <v>100</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>5</v>
+      <c r="F49" s="3">
+        <v>100</v>
       </c>
       <c r="G49" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
         <v>200</v>
@@ -4332,8 +4443,8 @@
       <c r="I49" s="3">
         <v>200</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
+      <c r="J49" s="3">
+        <v>200</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>5</v>
@@ -4341,8 +4452,8 @@
       <c r="L49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,31 +4720,34 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>16500</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>12600</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>16300</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>15900</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>300100</v>
+      </c>
+      <c r="E54" s="3">
         <v>308000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>326300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>318000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>327200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>332000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>333100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>323000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>313800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>330400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>357100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>355300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>352600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>337800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>339000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>285800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>293400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>278000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>292200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>258100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>258300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>259600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>262700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>268300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>265900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>260600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>256500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>270300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>236200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>236100</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,106 +5099,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>5</v>
+      <c r="D57" s="3">
+        <v>218400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>226700</v>
       </c>
       <c r="F57" s="3">
-        <v>200</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
+        <v>242600</v>
+      </c>
+      <c r="G57" s="3">
+        <v>241400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>245400</v>
+      </c>
+      <c r="I57" s="3">
+        <v>249000</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>235300</v>
       </c>
       <c r="K57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L57" s="3">
         <v>100</v>
       </c>
       <c r="M57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O57" s="3">
         <v>200</v>
       </c>
       <c r="P57" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S57" s="3">
         <v>400</v>
       </c>
       <c r="T57" s="3">
+        <v>400</v>
+      </c>
+      <c r="U57" s="3">
         <v>300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>200</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
-      </c>
       <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="3">
         <v>500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>200</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5082,7 +5216,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -5165,31 +5299,34 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -5263,31 +5400,34 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>218400</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>226700</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>242600</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>241800</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>245400</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>249000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>235300</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5361,31 +5501,34 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5459,31 +5602,34 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>224300</v>
+      </c>
+      <c r="E66" s="3">
         <v>233700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>252200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>243800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>253400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>256700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>257500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>244900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>236300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>246600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>263100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>259500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>255800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>238700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>235700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>183100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>191400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>177000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>230300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>196800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>197100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>198700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>202400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>208800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>206600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>201600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>197000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>235900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>201800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>202000</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,8 +6548,11 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6388,95 +6562,98 @@
       <c r="E72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="3">
         <v>43800</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K72" s="3">
         <v>42700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>42100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>41600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>40400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>40000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>39500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>39100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>38400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>37900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>37300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>37000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>36600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>36000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>35600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>35200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>35000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>34800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>34400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>34100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>33900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>34400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>34300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>34200</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>75800</v>
+      </c>
+      <c r="E76" s="3">
         <v>74300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>74100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>74300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>73700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>75400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>75500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>78100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>77500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>83900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>94000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>95800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>96800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>99100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>103300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>102600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>102000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>101000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>61900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>61300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>61200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>60800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>60400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>59500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>59300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>59000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>59500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>34400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>34300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>34200</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>700</v>
+      </c>
+      <c r="E81" s="3">
         <v>600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>500</v>
       </c>
-      <c r="F81" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>5</v>
+      <c r="G81" s="3">
+        <v>100</v>
+      </c>
+      <c r="H81" s="3">
+        <v>400</v>
       </c>
       <c r="I81" s="3">
         <v>500</v>
       </c>
       <c r="J81" s="3">
+        <v>500</v>
+      </c>
+      <c r="K81" s="3">
         <v>600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>400</v>
-      </c>
-      <c r="N81" s="3">
-        <v>500</v>
       </c>
       <c r="O81" s="3">
         <v>500</v>
       </c>
       <c r="P81" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q81" s="3">
         <v>700</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>500</v>
       </c>
       <c r="R81" s="3">
         <v>500</v>
       </c>
       <c r="S81" s="3">
+        <v>500</v>
+      </c>
+      <c r="T81" s="3">
         <v>800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>500</v>
-      </c>
-      <c r="V81" s="3">
-        <v>400</v>
       </c>
       <c r="W81" s="3">
         <v>400</v>
       </c>
       <c r="X81" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Y81" s="3">
         <v>200</v>
       </c>
       <c r="Z81" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA81" s="3">
         <v>300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-400</v>
       </c>
-      <c r="AD81" s="3">
-        <v>0</v>
-      </c>
       <c r="AE81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF81" s="3">
         <v>100</v>
       </c>
       <c r="AG81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-300</v>
       </c>
-      <c r="AH81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7216,14 +7415,14 @@
       <c r="F83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
+      <c r="G83" s="3">
+        <v>100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -7238,10 +7437,10 @@
         <v>100</v>
       </c>
       <c r="N83" s="3">
+        <v>100</v>
+      </c>
+      <c r="O83" s="3">
         <v>200</v>
-      </c>
-      <c r="O83" s="3">
-        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
@@ -7253,10 +7452,10 @@
         <v>100</v>
       </c>
       <c r="S83" s="3">
+        <v>100</v>
+      </c>
+      <c r="T83" s="3">
         <v>200</v>
-      </c>
-      <c r="T83" s="3">
-        <v>100</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,8 +8004,11 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7813,83 +8030,86 @@
       <c r="I89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
         <v>1300</v>
-      </c>
-      <c r="K89" s="3">
-        <v>900</v>
       </c>
       <c r="L89" s="3">
         <v>900</v>
       </c>
       <c r="M89" s="3">
+        <v>900</v>
+      </c>
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1000</v>
-      </c>
-      <c r="S89" s="3">
-        <v>1100</v>
       </c>
       <c r="T89" s="3">
         <v>1100</v>
       </c>
       <c r="U89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V89" s="3">
         <v>800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>-800</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,8 +8445,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8241,83 +8471,86 @@
       <c r="I94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
         <v>-13300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>19100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>9600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>17000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>38400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-19300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>6200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>6700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>3100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,31 +8585,32 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8767,106 +9013,109 @@
       <c r="I100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
         <v>6800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-15800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>14900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>14000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-15800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>34100</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-3600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>4900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-12600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>33600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-5200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-26300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>38600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>25300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>17600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>34000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-19800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-24500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>35200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-20400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>26400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FFBW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FFBW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
   <si>
     <t>FFBW</t>
   </si>
@@ -656,151 +656,154 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -808,10 +811,10 @@
         <v>3100</v>
       </c>
       <c r="E8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F8" s="3">
         <v>3000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2900</v>
       </c>
       <c r="G8" s="3">
         <v>2900</v>
@@ -820,49 +823,49 @@
         <v>2900</v>
       </c>
       <c r="I8" s="3">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="J8" s="3">
         <v>3000</v>
       </c>
       <c r="K8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L8" s="3">
         <v>3400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3000</v>
-      </c>
-      <c r="N8" s="3">
-        <v>2700</v>
       </c>
       <c r="O8" s="3">
         <v>2700</v>
       </c>
       <c r="P8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Q8" s="3">
         <v>2800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2900</v>
-      </c>
-      <c r="W8" s="3">
-        <v>2800</v>
       </c>
       <c r="X8" s="3">
         <v>2800</v>
@@ -874,34 +877,37 @@
         <v>2800</v>
       </c>
       <c r="AA8" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="AB8" s="3">
         <v>2700</v>
       </c>
       <c r="AC8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AD8" s="3">
         <v>2300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2200</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>2100</v>
       </c>
       <c r="AH8" s="3">
         <v>2100</v>
       </c>
       <c r="AI8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1001,8 +1007,11 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1010,10 +1019,10 @@
         <v>3100</v>
       </c>
       <c r="E10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F10" s="3">
         <v>3000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>2900</v>
       </c>
       <c r="G10" s="3">
         <v>2900</v>
@@ -1022,13 +1031,13 @@
         <v>2900</v>
       </c>
       <c r="I10" s="3">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="J10" s="3">
         <v>3000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
+      <c r="K10" s="3">
+        <v>3000</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
@@ -1102,8 +1111,11 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1151,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1253,11 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,8 +1357,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1367,8 +1386,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1442,8 +1461,11 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1469,7 +1491,7 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1543,8 +1565,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,13 +1602,14 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="E17" s="3">
         <v>2200</v>
@@ -1592,25 +1618,25 @@
         <v>2200</v>
       </c>
       <c r="G17" s="3">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="H17" s="3">
         <v>2400</v>
       </c>
       <c r="I17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J17" s="3">
         <v>2300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>300</v>
-      </c>
-      <c r="M17" s="3">
-        <v>200</v>
       </c>
       <c r="N17" s="3">
         <v>200</v>
@@ -1619,28 +1645,28 @@
         <v>200</v>
       </c>
       <c r="P17" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q17" s="3">
         <v>300</v>
       </c>
       <c r="R17" s="3">
+        <v>300</v>
+      </c>
+      <c r="S17" s="3">
         <v>500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>700</v>
-      </c>
-      <c r="W17" s="3">
-        <v>800</v>
       </c>
       <c r="X17" s="3">
         <v>800</v>
@@ -1649,48 +1675,51 @@
         <v>800</v>
       </c>
       <c r="Z17" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AA17" s="3">
         <v>700</v>
       </c>
       <c r="AB17" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC17" s="3">
         <v>600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>500</v>
-      </c>
-      <c r="AF17" s="3">
-        <v>400</v>
       </c>
       <c r="AG17" s="3">
         <v>400</v>
       </c>
       <c r="AH17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI17" s="3">
         <v>900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>600</v>
+      </c>
+      <c r="E18" s="3">
         <v>900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>600</v>
       </c>
       <c r="G18" s="3">
         <v>600</v>
@@ -1705,16 +1734,16 @@
         <v>600</v>
       </c>
       <c r="K18" s="3">
+        <v>600</v>
+      </c>
+      <c r="L18" s="3">
         <v>3000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2800</v>
-      </c>
-      <c r="N18" s="3">
-        <v>2500</v>
       </c>
       <c r="O18" s="3">
         <v>2500</v>
@@ -1723,25 +1752,25 @@
         <v>2500</v>
       </c>
       <c r="Q18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R18" s="3">
         <v>2900</v>
-      </c>
-      <c r="R18" s="3">
-        <v>2300</v>
       </c>
       <c r="S18" s="3">
         <v>2300</v>
       </c>
       <c r="T18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="U18" s="3">
         <v>4400</v>
-      </c>
-      <c r="U18" s="3">
-        <v>2200</v>
       </c>
       <c r="V18" s="3">
         <v>2200</v>
       </c>
       <c r="W18" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="X18" s="3">
         <v>2000</v>
@@ -1750,16 +1779,16 @@
         <v>2000</v>
       </c>
       <c r="Z18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA18" s="3">
         <v>2100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2100</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>1800</v>
       </c>
       <c r="AD18" s="3">
         <v>1800</v>
@@ -1771,16 +1800,19 @@
         <v>1800</v>
       </c>
       <c r="AG18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AH18" s="3">
         <v>1700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,8 +1848,9 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1842,41 +1875,41 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1700</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-1500</v>
       </c>
       <c r="W20" s="3">
         <v>-1500</v>
@@ -1885,141 +1918,147 @@
         <v>-1500</v>
       </c>
       <c r="Y20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-1600</v>
       </c>
       <c r="AC20" s="3">
         <v>-1600</v>
       </c>
       <c r="AD20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>-1600</v>
       </c>
       <c r="AG20" s="3">
         <v>-1600</v>
       </c>
       <c r="AH20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>700</v>
+      </c>
+      <c r="E21" s="3">
         <v>1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>900</v>
-      </c>
-      <c r="F21" s="3">
-        <v>700</v>
       </c>
       <c r="G21" s="3">
         <v>700</v>
       </c>
       <c r="H21" s="3">
+        <v>700</v>
+      </c>
+      <c r="I21" s="3">
         <v>600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>700</v>
       </c>
       <c r="J21" s="3">
         <v>700</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="K21" s="3">
+        <v>700</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="3">
         <v>800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>800</v>
-      </c>
-      <c r="W21" s="3">
-        <v>600</v>
       </c>
       <c r="X21" s="3">
         <v>600</v>
       </c>
       <c r="Y21" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="Z21" s="3">
         <v>400</v>
       </c>
       <c r="AA21" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AB21" s="3">
         <v>500</v>
       </c>
       <c r="AC21" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD21" s="3">
         <v>300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2044,8 +2083,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2119,19 +2158,22 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>600</v>
+      </c>
+      <c r="E23" s="3">
         <v>900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>800</v>
-      </c>
-      <c r="F23" s="3">
-        <v>600</v>
       </c>
       <c r="G23" s="3">
         <v>600</v>
@@ -2146,16 +2188,16 @@
         <v>600</v>
       </c>
       <c r="K23" s="3">
+        <v>600</v>
+      </c>
+      <c r="L23" s="3">
         <v>800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>900</v>
-      </c>
-      <c r="N23" s="3">
-        <v>600</v>
       </c>
       <c r="O23" s="3">
         <v>600</v>
@@ -2164,84 +2206,87 @@
         <v>600</v>
       </c>
       <c r="Q23" s="3">
+        <v>600</v>
+      </c>
+      <c r="R23" s="3">
         <v>900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>700</v>
-      </c>
-      <c r="W23" s="3">
-        <v>500</v>
       </c>
       <c r="X23" s="3">
         <v>500</v>
       </c>
       <c r="Y23" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="Z23" s="3">
         <v>300</v>
       </c>
       <c r="AA23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB23" s="3">
         <v>500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-200</v>
       </c>
-      <c r="AE23" s="3">
-        <v>0</v>
-      </c>
       <c r="AF23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG23" s="3">
         <v>100</v>
       </c>
       <c r="AH23" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI23" s="3">
         <v>-500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
-      </c>
-      <c r="E24" s="3">
-        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>100</v>
       </c>
       <c r="G24" s="3">
+        <v>100</v>
+      </c>
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>200</v>
       </c>
       <c r="J24" s="3">
         <v>200</v>
@@ -2259,31 +2304,31 @@
         <v>200</v>
       </c>
       <c r="O24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P24" s="3">
         <v>100</v>
       </c>
       <c r="Q24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R24" s="3">
         <v>200</v>
       </c>
       <c r="S24" s="3">
+        <v>200</v>
+      </c>
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
-      </c>
-      <c r="W24" s="3">
-        <v>100</v>
       </c>
       <c r="X24" s="3">
         <v>100</v>
@@ -2304,11 +2349,11 @@
         <v>100</v>
       </c>
       <c r="AD24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-100</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
         <v>0</v>
       </c>
@@ -2316,13 +2361,16 @@
         <v>0</v>
       </c>
       <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>-200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2470,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>500</v>
+      </c>
+      <c r="E26" s="3">
         <v>700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>400</v>
-      </c>
-      <c r="I26" s="3">
-        <v>500</v>
       </c>
       <c r="J26" s="3">
         <v>500</v>
       </c>
       <c r="K26" s="3">
+        <v>500</v>
+      </c>
+      <c r="L26" s="3">
         <v>600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>400</v>
-      </c>
-      <c r="O26" s="3">
-        <v>500</v>
       </c>
       <c r="P26" s="3">
         <v>500</v>
       </c>
       <c r="Q26" s="3">
+        <v>500</v>
+      </c>
+      <c r="R26" s="3">
         <v>700</v>
-      </c>
-      <c r="R26" s="3">
-        <v>500</v>
       </c>
       <c r="S26" s="3">
         <v>500</v>
       </c>
       <c r="T26" s="3">
+        <v>500</v>
+      </c>
+      <c r="U26" s="3">
         <v>800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>500</v>
-      </c>
-      <c r="W26" s="3">
-        <v>400</v>
       </c>
       <c r="X26" s="3">
         <v>400</v>
       </c>
       <c r="Y26" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Z26" s="3">
         <v>200</v>
       </c>
       <c r="AA26" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB26" s="3">
         <v>300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-100</v>
       </c>
-      <c r="AE26" s="3">
-        <v>0</v>
-      </c>
       <c r="AF26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG26" s="3">
         <v>100</v>
       </c>
       <c r="AH26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI26" s="3">
         <v>-300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>500</v>
+      </c>
+      <c r="E27" s="3">
         <v>700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>400</v>
-      </c>
-      <c r="I27" s="3">
-        <v>500</v>
       </c>
       <c r="J27" s="3">
         <v>500</v>
       </c>
       <c r="K27" s="3">
+        <v>500</v>
+      </c>
+      <c r="L27" s="3">
         <v>600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>400</v>
-      </c>
-      <c r="O27" s="3">
-        <v>500</v>
       </c>
       <c r="P27" s="3">
         <v>500</v>
       </c>
       <c r="Q27" s="3">
+        <v>500</v>
+      </c>
+      <c r="R27" s="3">
         <v>700</v>
-      </c>
-      <c r="R27" s="3">
-        <v>500</v>
       </c>
       <c r="S27" s="3">
         <v>500</v>
       </c>
       <c r="T27" s="3">
+        <v>500</v>
+      </c>
+      <c r="U27" s="3">
         <v>800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>500</v>
-      </c>
-      <c r="W27" s="3">
-        <v>400</v>
       </c>
       <c r="X27" s="3">
         <v>400</v>
       </c>
       <c r="Y27" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Z27" s="3">
         <v>200</v>
       </c>
       <c r="AA27" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB27" s="3">
         <v>300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-100</v>
       </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
       <c r="AF27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG27" s="3">
         <v>100</v>
       </c>
       <c r="AH27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI27" s="3">
         <v>-300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2782,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2790,17 +2850,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -2808,12 +2868,12 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-400</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2826,8 +2886,11 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2990,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,8 +3094,11 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3054,41 +3123,41 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1700</v>
-      </c>
-      <c r="V32" s="3">
-        <v>1500</v>
       </c>
       <c r="W32" s="3">
         <v>1500</v>
@@ -3097,141 +3166,147 @@
         <v>1500</v>
       </c>
       <c r="Y32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1500</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>1600</v>
       </c>
       <c r="AC32" s="3">
         <v>1600</v>
       </c>
       <c r="AD32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AE32" s="3">
         <v>1900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1800</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>1600</v>
       </c>
       <c r="AG32" s="3">
         <v>1600</v>
       </c>
       <c r="AH32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AI32" s="3">
         <v>1700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>500</v>
+      </c>
+      <c r="E33" s="3">
         <v>700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>400</v>
-      </c>
-      <c r="I33" s="3">
-        <v>500</v>
       </c>
       <c r="J33" s="3">
         <v>500</v>
       </c>
       <c r="K33" s="3">
+        <v>500</v>
+      </c>
+      <c r="L33" s="3">
         <v>600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>400</v>
-      </c>
-      <c r="O33" s="3">
-        <v>500</v>
       </c>
       <c r="P33" s="3">
         <v>500</v>
       </c>
       <c r="Q33" s="3">
+        <v>500</v>
+      </c>
+      <c r="R33" s="3">
         <v>700</v>
-      </c>
-      <c r="R33" s="3">
-        <v>500</v>
       </c>
       <c r="S33" s="3">
         <v>500</v>
       </c>
       <c r="T33" s="3">
+        <v>500</v>
+      </c>
+      <c r="U33" s="3">
         <v>800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>500</v>
-      </c>
-      <c r="W33" s="3">
-        <v>400</v>
       </c>
       <c r="X33" s="3">
         <v>400</v>
       </c>
       <c r="Y33" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Z33" s="3">
         <v>200</v>
       </c>
       <c r="AA33" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB33" s="3">
         <v>300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-400</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
       <c r="AF33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG33" s="3">
         <v>100</v>
       </c>
       <c r="AH33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI33" s="3">
         <v>-300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3406,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>500</v>
+      </c>
+      <c r="E35" s="3">
         <v>700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>400</v>
-      </c>
-      <c r="I35" s="3">
-        <v>500</v>
       </c>
       <c r="J35" s="3">
         <v>500</v>
       </c>
       <c r="K35" s="3">
+        <v>500</v>
+      </c>
+      <c r="L35" s="3">
         <v>600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>400</v>
-      </c>
-      <c r="O35" s="3">
-        <v>500</v>
       </c>
       <c r="P35" s="3">
         <v>500</v>
       </c>
       <c r="Q35" s="3">
+        <v>500</v>
+      </c>
+      <c r="R35" s="3">
         <v>700</v>
-      </c>
-      <c r="R35" s="3">
-        <v>500</v>
       </c>
       <c r="S35" s="3">
         <v>500</v>
       </c>
       <c r="T35" s="3">
+        <v>500</v>
+      </c>
+      <c r="U35" s="3">
         <v>800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>500</v>
-      </c>
-      <c r="W35" s="3">
-        <v>400</v>
       </c>
       <c r="X35" s="3">
         <v>400</v>
       </c>
       <c r="Y35" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Z35" s="3">
         <v>200</v>
       </c>
       <c r="AA35" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB35" s="3">
         <v>300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-400</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
       <c r="AF35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG35" s="3">
         <v>100</v>
       </c>
       <c r="AH35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI35" s="3">
         <v>-300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3659,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3697,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E41" s="3">
         <v>14800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>30900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>52500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>71000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>62000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>50700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>41500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5000</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3728,11 +3817,11 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>200</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -3740,82 +3829,85 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>2000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>13400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>16600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>11600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>25600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>13900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>9200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>18200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>5400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>37100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>11000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>13000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>33700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>3500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2000</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI42" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ42" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3840,8 +3932,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3915,8 +4007,11 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3941,8 +4036,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4016,8 +4111,11 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4030,20 +4128,20 @@
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -4117,35 +4215,38 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E46" s="3">
         <v>14800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11400</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4218,35 +4319,38 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E47" s="3">
         <v>37600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>38000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>40100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>42600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>40300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>43700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>45700</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4319,43 +4423,46 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6300</v>
+        <v>6200</v>
       </c>
       <c r="E48" s="3">
         <v>6300</v>
       </c>
       <c r="F48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="G48" s="3">
         <v>6400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6600</v>
-      </c>
-      <c r="K48" s="3">
-        <v>6700</v>
       </c>
       <c r="L48" s="3">
         <v>6700</v>
       </c>
       <c r="M48" s="3">
+        <v>6700</v>
+      </c>
+      <c r="N48" s="3">
         <v>5900</v>
-      </c>
-      <c r="N48" s="3">
-        <v>5500</v>
       </c>
       <c r="O48" s="3">
         <v>5500</v>
@@ -4364,64 +4471,67 @@
         <v>5500</v>
       </c>
       <c r="Q48" s="3">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="R48" s="3">
         <v>5600</v>
       </c>
       <c r="S48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="T48" s="3">
         <v>4600</v>
-      </c>
-      <c r="T48" s="3">
-        <v>4700</v>
       </c>
       <c r="U48" s="3">
         <v>4700</v>
       </c>
       <c r="V48" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="W48" s="3">
         <v>4800</v>
       </c>
       <c r="X48" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Y48" s="3">
         <v>4900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5000</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>5100</v>
       </c>
       <c r="AA48" s="3">
         <v>5100</v>
       </c>
       <c r="AB48" s="3">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="AC48" s="3">
         <v>5200</v>
       </c>
       <c r="AD48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AE48" s="3">
         <v>5300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7700</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI48" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4435,10 +4545,10 @@
         <v>100</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H49" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
         <v>200</v>
@@ -4446,8 +4556,8 @@
       <c r="J49" s="3">
         <v>200</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
+      <c r="K49" s="3">
+        <v>200</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>5</v>
@@ -4455,8 +4565,8 @@
       <c r="M49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -4521,8 +4631,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4735,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,35 +4839,38 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E52" s="3">
         <v>16000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16000</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -4824,8 +4943,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5047,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>287900</v>
+      </c>
+      <c r="E54" s="3">
         <v>300100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>308000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>326300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>318000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>327200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>332000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>333100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>323000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>313800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>330400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>357100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>355300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>352600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>337800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>339000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>285800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>293400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>278000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>292200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>258100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>258300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>259600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>262700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>268300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>265900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>260600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>256500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>270300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>236200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>236100</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI54" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5191,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,109 +5229,113 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>208700</v>
+      </c>
+      <c r="E57" s="3">
         <v>218400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>226700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>242600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>241400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>245400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>249000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>235300</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
       </c>
       <c r="N57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
       </c>
       <c r="Q57" s="3">
+        <v>200</v>
+      </c>
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T57" s="3">
         <v>400</v>
       </c>
       <c r="U57" s="3">
+        <v>400</v>
+      </c>
+      <c r="V57" s="3">
         <v>300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>200</v>
       </c>
-      <c r="AD57" s="3">
-        <v>0</v>
-      </c>
       <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="3">
         <v>500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>200</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI57" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5216,11 +5349,11 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -5302,8 +5435,11 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5328,8 +5464,8 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -5403,35 +5539,38 @@
       <c r="AI59" s="3">
         <v>0</v>
       </c>
+      <c r="AJ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>208700</v>
+      </c>
+      <c r="E60" s="3">
         <v>218400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>226700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>242600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>241800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>245400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>249000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>235300</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5504,35 +5643,38 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>3000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>500</v>
-      </c>
-      <c r="H61" s="3">
-        <v>5000</v>
       </c>
       <c r="I61" s="3">
         <v>5000</v>
       </c>
       <c r="J61" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K61" s="3">
         <v>20000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5605,35 +5747,38 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E62" s="3">
         <v>2800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2200</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5706,8 +5851,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5955,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6059,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6163,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>212100</v>
+      </c>
+      <c r="E66" s="3">
         <v>224300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>233700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>252200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>243800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>253400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>256700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>257500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>244900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>236300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>246600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>263100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>259500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>255800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>238700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>235700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>183100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>191400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>177000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>230300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>196800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>197100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>198700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>202400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>208800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>206600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>201600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>197000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>235900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>201800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>202000</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI66" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6307,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6409,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6513,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6617,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,8 +6721,11 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6565,95 +6738,98 @@
       <c r="F72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="3">
         <v>43800</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L72" s="3">
         <v>42700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>42100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>41600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>40400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>40000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>39500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>39100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>38400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>37900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>37300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>37000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>36600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>36000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>35600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>35200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>35000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>34800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>34400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>34100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>33900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>34400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>34300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>34200</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI72" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6929,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7033,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,8 +7137,11 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6964,100 +7149,103 @@
         <v>75800</v>
       </c>
       <c r="E76" s="3">
+        <v>75800</v>
+      </c>
+      <c r="F76" s="3">
         <v>74300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>74100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>74300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>73700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>75400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>75500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>78100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>77500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>83900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>94000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>95800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>96800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>99100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>103300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>102600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>102000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>101000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>61900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>61300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>61200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>60800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>60400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>59500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>59300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>59000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>59500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>34400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>34300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>34200</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI76" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7345,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>500</v>
+      </c>
+      <c r="E81" s="3">
         <v>700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>400</v>
-      </c>
-      <c r="I81" s="3">
-        <v>500</v>
       </c>
       <c r="J81" s="3">
         <v>500</v>
       </c>
       <c r="K81" s="3">
+        <v>500</v>
+      </c>
+      <c r="L81" s="3">
         <v>600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>400</v>
-      </c>
-      <c r="O81" s="3">
-        <v>500</v>
       </c>
       <c r="P81" s="3">
         <v>500</v>
       </c>
       <c r="Q81" s="3">
+        <v>500</v>
+      </c>
+      <c r="R81" s="3">
         <v>700</v>
-      </c>
-      <c r="R81" s="3">
-        <v>500</v>
       </c>
       <c r="S81" s="3">
         <v>500</v>
       </c>
       <c r="T81" s="3">
+        <v>500</v>
+      </c>
+      <c r="U81" s="3">
         <v>800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>500</v>
-      </c>
-      <c r="W81" s="3">
-        <v>400</v>
       </c>
       <c r="X81" s="3">
         <v>400</v>
       </c>
       <c r="Y81" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Z81" s="3">
         <v>200</v>
       </c>
       <c r="AA81" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB81" s="3">
         <v>300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-400</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
       <c r="AF81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG81" s="3">
         <v>100</v>
       </c>
       <c r="AH81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI81" s="3">
         <v>-300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7598,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7415,8 +7613,8 @@
       <c r="F83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G83" s="3">
-        <v>100</v>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -7440,10 +7638,10 @@
         <v>100</v>
       </c>
       <c r="O83" s="3">
+        <v>100</v>
+      </c>
+      <c r="P83" s="3">
         <v>200</v>
-      </c>
-      <c r="P83" s="3">
-        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
@@ -7455,10 +7653,10 @@
         <v>100</v>
       </c>
       <c r="T83" s="3">
+        <v>100</v>
+      </c>
+      <c r="U83" s="3">
         <v>200</v>
-      </c>
-      <c r="U83" s="3">
-        <v>100</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
@@ -7502,8 +7700,11 @@
       <c r="AI83" s="3">
         <v>100</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7804,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7908,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8012,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8116,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,8 +8220,11 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8033,83 +8249,86 @@
       <c r="J89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
         <v>1300</v>
-      </c>
-      <c r="L89" s="3">
-        <v>900</v>
       </c>
       <c r="M89" s="3">
         <v>900</v>
       </c>
       <c r="N89" s="3">
+        <v>900</v>
+      </c>
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1000</v>
-      </c>
-      <c r="T89" s="3">
-        <v>1100</v>
       </c>
       <c r="U89" s="3">
         <v>1100</v>
       </c>
       <c r="V89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W89" s="3">
         <v>800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,8 +8364,9 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8171,8 +8391,8 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8205,11 +8425,11 @@
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
@@ -8229,25 +8449,28 @@
         <v>0</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-200</v>
       </c>
-      <c r="AH91" s="3">
-        <v>0</v>
-      </c>
       <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8570,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,8 +8674,11 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8474,83 +8703,86 @@
       <c r="J94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
         <v>-13300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>19100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>9600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>17000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>38400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-19300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>6200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>6700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>3100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +8818,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8612,8 +8845,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8687,8 +8920,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9024,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9128,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,8 +9232,11 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9016,83 +9261,86 @@
       <c r="J100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
         <v>6800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-15800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>14900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>14000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-15800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>34100</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>4600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-12600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>33600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9117,8 +9365,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9192,8 +9440,11 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9219,78 +9470,81 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-5200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-26300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>38600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>25300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>17600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>34000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-12200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-19800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-24500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>35200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-20400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>26400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FFBW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FFBW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
   <si>
     <t>FFBW</t>
   </si>
@@ -656,168 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="E8" s="3">
         <v>3100</v>
       </c>
       <c r="F8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G8" s="3">
         <v>3000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>2900</v>
       </c>
       <c r="H8" s="3">
         <v>2900</v>
@@ -826,49 +830,49 @@
         <v>2900</v>
       </c>
       <c r="J8" s="3">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="K8" s="3">
         <v>3000</v>
       </c>
       <c r="L8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M8" s="3">
         <v>3400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3000</v>
-      </c>
-      <c r="O8" s="3">
-        <v>2700</v>
       </c>
       <c r="P8" s="3">
         <v>2700</v>
       </c>
       <c r="Q8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="R8" s="3">
         <v>2800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2900</v>
-      </c>
-      <c r="X8" s="3">
-        <v>2800</v>
       </c>
       <c r="Y8" s="3">
         <v>2800</v>
@@ -880,34 +884,37 @@
         <v>2800</v>
       </c>
       <c r="AB8" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="AC8" s="3">
         <v>2700</v>
       </c>
       <c r="AD8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AE8" s="3">
         <v>2300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2200</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>2100</v>
       </c>
       <c r="AI8" s="3">
         <v>2100</v>
       </c>
       <c r="AJ8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AK8" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1010,22 +1017,25 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="E10" s="3">
         <v>3100</v>
       </c>
       <c r="F10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G10" s="3">
         <v>3000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2900</v>
       </c>
       <c r="H10" s="3">
         <v>2900</v>
@@ -1034,13 +1044,13 @@
         <v>2900</v>
       </c>
       <c r="J10" s="3">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="K10" s="3">
         <v>3000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
+      <c r="L10" s="3">
+        <v>3000</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
@@ -1114,8 +1124,11 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1152,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1256,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1360,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1389,8 +1409,8 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1464,8 +1484,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1494,7 +1517,7 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1568,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1603,8 +1629,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1612,7 +1639,7 @@
         <v>2400</v>
       </c>
       <c r="E17" s="3">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="F17" s="3">
         <v>2200</v>
@@ -1621,25 +1648,25 @@
         <v>2200</v>
       </c>
       <c r="H17" s="3">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="I17" s="3">
         <v>2400</v>
       </c>
       <c r="J17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K17" s="3">
         <v>2300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
-      </c>
-      <c r="N17" s="3">
-        <v>200</v>
       </c>
       <c r="O17" s="3">
         <v>200</v>
@@ -1648,28 +1675,28 @@
         <v>200</v>
       </c>
       <c r="Q17" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R17" s="3">
         <v>300</v>
       </c>
       <c r="S17" s="3">
+        <v>300</v>
+      </c>
+      <c r="T17" s="3">
         <v>500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>700</v>
-      </c>
-      <c r="X17" s="3">
-        <v>800</v>
       </c>
       <c r="Y17" s="3">
         <v>800</v>
@@ -1678,37 +1705,40 @@
         <v>800</v>
       </c>
       <c r="AA17" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AB17" s="3">
         <v>700</v>
       </c>
       <c r="AC17" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD17" s="3">
         <v>600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>500</v>
-      </c>
-      <c r="AG17" s="3">
-        <v>400</v>
       </c>
       <c r="AH17" s="3">
         <v>400</v>
       </c>
       <c r="AI17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1716,13 +1746,13 @@
         <v>600</v>
       </c>
       <c r="E18" s="3">
+        <v>600</v>
+      </c>
+      <c r="F18" s="3">
         <v>900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>600</v>
       </c>
       <c r="H18" s="3">
         <v>600</v>
@@ -1737,16 +1767,16 @@
         <v>600</v>
       </c>
       <c r="L18" s="3">
+        <v>600</v>
+      </c>
+      <c r="M18" s="3">
         <v>3000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2800</v>
-      </c>
-      <c r="O18" s="3">
-        <v>2500</v>
       </c>
       <c r="P18" s="3">
         <v>2500</v>
@@ -1755,25 +1785,25 @@
         <v>2500</v>
       </c>
       <c r="R18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="S18" s="3">
         <v>2900</v>
-      </c>
-      <c r="S18" s="3">
-        <v>2300</v>
       </c>
       <c r="T18" s="3">
         <v>2300</v>
       </c>
       <c r="U18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="V18" s="3">
         <v>4400</v>
-      </c>
-      <c r="V18" s="3">
-        <v>2200</v>
       </c>
       <c r="W18" s="3">
         <v>2200</v>
       </c>
       <c r="X18" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="Y18" s="3">
         <v>2000</v>
@@ -1782,16 +1812,16 @@
         <v>2000</v>
       </c>
       <c r="AA18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AB18" s="3">
         <v>2100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2100</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>1800</v>
       </c>
       <c r="AE18" s="3">
         <v>1800</v>
@@ -1803,16 +1833,19 @@
         <v>1800</v>
       </c>
       <c r="AH18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AI18" s="3">
         <v>1700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1849,8 +1882,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1878,41 +1912,41 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1700</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-1500</v>
       </c>
       <c r="X20" s="3">
         <v>-1500</v>
@@ -1921,40 +1955,43 @@
         <v>-1500</v>
       </c>
       <c r="Z20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-1600</v>
       </c>
       <c r="AD20" s="3">
         <v>-1600</v>
       </c>
       <c r="AE20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-1600</v>
       </c>
       <c r="AH20" s="3">
         <v>-1600</v>
       </c>
       <c r="AI20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1962,103 +1999,106 @@
         <v>700</v>
       </c>
       <c r="E21" s="3">
+        <v>700</v>
+      </c>
+      <c r="F21" s="3">
         <v>1000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>700</v>
       </c>
       <c r="H21" s="3">
         <v>700</v>
       </c>
       <c r="I21" s="3">
+        <v>700</v>
+      </c>
+      <c r="J21" s="3">
         <v>600</v>
-      </c>
-      <c r="J21" s="3">
-        <v>700</v>
       </c>
       <c r="K21" s="3">
         <v>700</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="L21" s="3">
+        <v>700</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3">
         <v>800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>800</v>
-      </c>
-      <c r="X21" s="3">
-        <v>600</v>
       </c>
       <c r="Y21" s="3">
         <v>600</v>
       </c>
       <c r="Z21" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AA21" s="3">
         <v>400</v>
       </c>
       <c r="AB21" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AC21" s="3">
         <v>500</v>
       </c>
       <c r="AD21" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE21" s="3">
         <v>300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2086,8 +2126,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2161,8 +2201,11 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2170,13 +2213,13 @@
         <v>600</v>
       </c>
       <c r="E23" s="3">
+        <v>600</v>
+      </c>
+      <c r="F23" s="3">
         <v>900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>600</v>
       </c>
       <c r="H23" s="3">
         <v>600</v>
@@ -2191,16 +2234,16 @@
         <v>600</v>
       </c>
       <c r="L23" s="3">
+        <v>600</v>
+      </c>
+      <c r="M23" s="3">
         <v>800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>900</v>
-      </c>
-      <c r="O23" s="3">
-        <v>600</v>
       </c>
       <c r="P23" s="3">
         <v>600</v>
@@ -2209,64 +2252,67 @@
         <v>600</v>
       </c>
       <c r="R23" s="3">
+        <v>600</v>
+      </c>
+      <c r="S23" s="3">
         <v>900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>700</v>
-      </c>
-      <c r="X23" s="3">
-        <v>500</v>
       </c>
       <c r="Y23" s="3">
         <v>500</v>
       </c>
       <c r="Z23" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AA23" s="3">
         <v>300</v>
       </c>
       <c r="AB23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC23" s="3">
         <v>500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-200</v>
       </c>
-      <c r="AF23" s="3">
-        <v>0</v>
-      </c>
       <c r="AG23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH23" s="3">
         <v>100</v>
       </c>
       <c r="AI23" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2274,22 +2320,22 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
-      </c>
-      <c r="F24" s="3">
-        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
       </c>
       <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>200</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
@@ -2307,31 +2353,31 @@
         <v>200</v>
       </c>
       <c r="P24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q24" s="3">
         <v>100</v>
       </c>
       <c r="R24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S24" s="3">
         <v>200</v>
       </c>
       <c r="T24" s="3">
+        <v>200</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>200</v>
-      </c>
-      <c r="X24" s="3">
-        <v>100</v>
       </c>
       <c r="Y24" s="3">
         <v>100</v>
@@ -2352,11 +2398,11 @@
         <v>100</v>
       </c>
       <c r="AE24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF24" s="3">
         <v>-100</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
       <c r="AG24" s="3">
         <v>0</v>
       </c>
@@ -2364,13 +2410,16 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2473,8 +2522,11 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2482,103 +2534,106 @@
         <v>500</v>
       </c>
       <c r="E26" s="3">
+        <v>500</v>
+      </c>
+      <c r="F26" s="3">
         <v>700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>400</v>
-      </c>
-      <c r="J26" s="3">
-        <v>500</v>
       </c>
       <c r="K26" s="3">
         <v>500</v>
       </c>
       <c r="L26" s="3">
+        <v>500</v>
+      </c>
+      <c r="M26" s="3">
         <v>600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>400</v>
-      </c>
-      <c r="P26" s="3">
-        <v>500</v>
       </c>
       <c r="Q26" s="3">
         <v>500</v>
       </c>
       <c r="R26" s="3">
+        <v>500</v>
+      </c>
+      <c r="S26" s="3">
         <v>700</v>
-      </c>
-      <c r="S26" s="3">
-        <v>500</v>
       </c>
       <c r="T26" s="3">
         <v>500</v>
       </c>
       <c r="U26" s="3">
+        <v>500</v>
+      </c>
+      <c r="V26" s="3">
         <v>800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>500</v>
-      </c>
-      <c r="X26" s="3">
-        <v>400</v>
       </c>
       <c r="Y26" s="3">
         <v>400</v>
       </c>
       <c r="Z26" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AA26" s="3">
         <v>200</v>
       </c>
       <c r="AB26" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC26" s="3">
         <v>300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-100</v>
       </c>
-      <c r="AF26" s="3">
-        <v>0</v>
-      </c>
       <c r="AG26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH26" s="3">
         <v>100</v>
       </c>
       <c r="AI26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2586,103 +2641,106 @@
         <v>500</v>
       </c>
       <c r="E27" s="3">
+        <v>500</v>
+      </c>
+      <c r="F27" s="3">
         <v>700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>400</v>
-      </c>
-      <c r="J27" s="3">
-        <v>500</v>
       </c>
       <c r="K27" s="3">
         <v>500</v>
       </c>
       <c r="L27" s="3">
+        <v>500</v>
+      </c>
+      <c r="M27" s="3">
         <v>600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>400</v>
-      </c>
-      <c r="P27" s="3">
-        <v>500</v>
       </c>
       <c r="Q27" s="3">
         <v>500</v>
       </c>
       <c r="R27" s="3">
+        <v>500</v>
+      </c>
+      <c r="S27" s="3">
         <v>700</v>
-      </c>
-      <c r="S27" s="3">
-        <v>500</v>
       </c>
       <c r="T27" s="3">
         <v>500</v>
       </c>
       <c r="U27" s="3">
+        <v>500</v>
+      </c>
+      <c r="V27" s="3">
         <v>800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>500</v>
-      </c>
-      <c r="X27" s="3">
-        <v>400</v>
       </c>
       <c r="Y27" s="3">
         <v>400</v>
       </c>
       <c r="Z27" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AA27" s="3">
         <v>200</v>
       </c>
       <c r="AB27" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC27" s="3">
         <v>300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-100</v>
       </c>
-      <c r="AF27" s="3">
-        <v>0</v>
-      </c>
       <c r="AG27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH27" s="3">
         <v>100</v>
       </c>
       <c r="AI27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2785,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2853,17 +2914,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
@@ -2871,12 +2932,12 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-400</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2889,8 +2950,11 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2993,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3097,8 +3164,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3126,41 +3196,41 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1700</v>
-      </c>
-      <c r="W32" s="3">
-        <v>1500</v>
       </c>
       <c r="X32" s="3">
         <v>1500</v>
@@ -3169,40 +3239,43 @@
         <v>1500</v>
       </c>
       <c r="Z32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA32" s="3">
         <v>1700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1500</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>1600</v>
       </c>
       <c r="AD32" s="3">
         <v>1600</v>
       </c>
       <c r="AE32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AF32" s="3">
         <v>1900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1800</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>1600</v>
       </c>
       <c r="AH32" s="3">
         <v>1600</v>
       </c>
       <c r="AI32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3210,103 +3283,106 @@
         <v>500</v>
       </c>
       <c r="E33" s="3">
+        <v>500</v>
+      </c>
+      <c r="F33" s="3">
         <v>700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>400</v>
-      </c>
-      <c r="J33" s="3">
-        <v>500</v>
       </c>
       <c r="K33" s="3">
         <v>500</v>
       </c>
       <c r="L33" s="3">
+        <v>500</v>
+      </c>
+      <c r="M33" s="3">
         <v>600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>400</v>
-      </c>
-      <c r="P33" s="3">
-        <v>500</v>
       </c>
       <c r="Q33" s="3">
         <v>500</v>
       </c>
       <c r="R33" s="3">
+        <v>500</v>
+      </c>
+      <c r="S33" s="3">
         <v>700</v>
-      </c>
-      <c r="S33" s="3">
-        <v>500</v>
       </c>
       <c r="T33" s="3">
         <v>500</v>
       </c>
       <c r="U33" s="3">
+        <v>500</v>
+      </c>
+      <c r="V33" s="3">
         <v>800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>500</v>
-      </c>
-      <c r="X33" s="3">
-        <v>400</v>
       </c>
       <c r="Y33" s="3">
         <v>400</v>
       </c>
       <c r="Z33" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AA33" s="3">
         <v>200</v>
       </c>
       <c r="AB33" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC33" s="3">
         <v>300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-400</v>
       </c>
-      <c r="AF33" s="3">
-        <v>0</v>
-      </c>
       <c r="AG33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH33" s="3">
         <v>100</v>
       </c>
       <c r="AI33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3409,8 +3485,11 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3418,212 +3497,218 @@
         <v>500</v>
       </c>
       <c r="E35" s="3">
+        <v>500</v>
+      </c>
+      <c r="F35" s="3">
         <v>700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>400</v>
-      </c>
-      <c r="J35" s="3">
-        <v>500</v>
       </c>
       <c r="K35" s="3">
         <v>500</v>
       </c>
       <c r="L35" s="3">
+        <v>500</v>
+      </c>
+      <c r="M35" s="3">
         <v>600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>400</v>
-      </c>
-      <c r="P35" s="3">
-        <v>500</v>
       </c>
       <c r="Q35" s="3">
         <v>500</v>
       </c>
       <c r="R35" s="3">
+        <v>500</v>
+      </c>
+      <c r="S35" s="3">
         <v>700</v>
-      </c>
-      <c r="S35" s="3">
-        <v>500</v>
       </c>
       <c r="T35" s="3">
         <v>500</v>
       </c>
       <c r="U35" s="3">
+        <v>500</v>
+      </c>
+      <c r="V35" s="3">
         <v>800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>500</v>
-      </c>
-      <c r="X35" s="3">
-        <v>400</v>
       </c>
       <c r="Y35" s="3">
         <v>400</v>
       </c>
       <c r="Z35" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AA35" s="3">
         <v>200</v>
       </c>
       <c r="AB35" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC35" s="3">
         <v>300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-400</v>
       </c>
-      <c r="AF35" s="3">
-        <v>0</v>
-      </c>
       <c r="AG35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH35" s="3">
         <v>100</v>
       </c>
       <c r="AI35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3660,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3698,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E41" s="3">
         <v>6100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>52500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>71000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>62000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>50700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>41500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5000</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3820,11 +3910,11 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>200</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -3832,82 +3922,85 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>2000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>16600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>11600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>25600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>13900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>9200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>18200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>5400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>37100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>11000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>13000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>33700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2000</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ42" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3935,8 +4028,8 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -4010,8 +4103,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4039,8 +4135,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4114,8 +4210,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4131,20 +4230,20 @@
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -4218,38 +4317,41 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>238100</v>
+      </c>
+      <c r="E46" s="3">
         <v>6100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11400</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4322,38 +4424,41 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E47" s="3">
         <v>34900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>37600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>38000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>40100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>42600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>40300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>43700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>45700</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4426,46 +4531,49 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6200</v>
-      </c>
-      <c r="E48" s="3">
-        <v>6300</v>
       </c>
       <c r="F48" s="3">
         <v>6300</v>
       </c>
       <c r="G48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H48" s="3">
         <v>6400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6600</v>
-      </c>
-      <c r="L48" s="3">
-        <v>6700</v>
       </c>
       <c r="M48" s="3">
         <v>6700</v>
       </c>
       <c r="N48" s="3">
+        <v>6700</v>
+      </c>
+      <c r="O48" s="3">
         <v>5900</v>
-      </c>
-      <c r="O48" s="3">
-        <v>5500</v>
       </c>
       <c r="P48" s="3">
         <v>5500</v>
@@ -4474,64 +4582,67 @@
         <v>5500</v>
       </c>
       <c r="R48" s="3">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="S48" s="3">
         <v>5600</v>
       </c>
       <c r="T48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="U48" s="3">
         <v>4600</v>
-      </c>
-      <c r="U48" s="3">
-        <v>4700</v>
       </c>
       <c r="V48" s="3">
         <v>4700</v>
       </c>
       <c r="W48" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="X48" s="3">
         <v>4800</v>
       </c>
       <c r="Y48" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Z48" s="3">
         <v>4900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5000</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>5100</v>
       </c>
       <c r="AB48" s="3">
         <v>5100</v>
       </c>
       <c r="AC48" s="3">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="AD48" s="3">
         <v>5200</v>
       </c>
       <c r="AE48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AF48" s="3">
         <v>5300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7700</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ48" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4548,10 +4659,10 @@
         <v>100</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I49" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>200</v>
@@ -4559,8 +4670,8 @@
       <c r="K49" s="3">
         <v>200</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
+      <c r="L49" s="3">
+        <v>200</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>5</v>
@@ -4568,8 +4679,8 @@
       <c r="N49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -4634,8 +4745,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4738,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4842,38 +4959,41 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E52" s="3">
         <v>16100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16000</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -4946,8 +5066,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5050,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>294800</v>
+      </c>
+      <c r="E54" s="3">
         <v>287900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>300100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>308000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>326300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>318000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>327200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>332000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>333100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>323000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>313800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>330400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>357100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>355300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>352600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>337800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>339000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>285800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>293400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>278000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>292200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>258100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>258300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>259600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>262700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>268300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>265900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>260600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>256500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>270300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>236200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>236100</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5192,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5230,112 +5360,116 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>219000</v>
+      </c>
+      <c r="E57" s="3">
         <v>208700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>218400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>226700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>242600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>241400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>245400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>249000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>235300</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N57" s="3">
         <v>100</v>
       </c>
       <c r="O57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="3">
         <v>200</v>
       </c>
       <c r="R57" s="3">
+        <v>200</v>
+      </c>
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
       <c r="T57" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U57" s="3">
         <v>400</v>
       </c>
       <c r="V57" s="3">
+        <v>400</v>
+      </c>
+      <c r="W57" s="3">
         <v>300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>200</v>
       </c>
-      <c r="AE57" s="3">
-        <v>0</v>
-      </c>
       <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="3">
         <v>500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>200</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ57" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5352,11 +5486,11 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -5438,8 +5572,11 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5467,8 +5604,8 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -5542,38 +5679,41 @@
       <c r="AJ59" s="3">
         <v>0</v>
       </c>
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>219000</v>
+      </c>
+      <c r="E60" s="3">
         <v>208700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>218400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>226700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>242600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>241800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>245400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>249000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>235300</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5646,8 +5786,11 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5655,29 +5798,29 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>3000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>500</v>
-      </c>
-      <c r="I61" s="3">
-        <v>5000</v>
       </c>
       <c r="J61" s="3">
         <v>5000</v>
       </c>
       <c r="K61" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L61" s="3">
         <v>20000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5750,38 +5893,41 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E62" s="3">
         <v>3500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2200</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -5854,8 +6000,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5958,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6062,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6166,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>221700</v>
+      </c>
+      <c r="E66" s="3">
         <v>212100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>224300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>233700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>252200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>243800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>253400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>256700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>257500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>244900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>236300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>246600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>263100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>259500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>255800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>238700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>235700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>183100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>191400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>177000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>230300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>196800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>197100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>198700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>202400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>208800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>206600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>201600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>197000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>235900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>201800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>202000</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6308,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6412,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6516,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6620,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6724,8 +6895,11 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6741,95 +6915,98 @@
       <c r="G72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I72" s="3">
         <v>43800</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M72" s="3">
         <v>42700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>42100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>41600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>40400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>40000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>39500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>39100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>38400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>37900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>37300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>37000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>36600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>36000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>35600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>35200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>35000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>34800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>34400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>34100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>33900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>34400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>34300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>34200</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6932,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7036,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7140,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>75800</v>
+        <v>73100</v>
       </c>
       <c r="E76" s="3">
         <v>75800</v>
       </c>
       <c r="F76" s="3">
+        <v>75800</v>
+      </c>
+      <c r="G76" s="3">
         <v>74300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>74100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>74300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>73700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>75400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>75500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>78100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>77500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>83900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>94000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>95800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>96800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>99100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>103300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>102600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>102000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>101000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>61900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>61300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>61200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>60800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>60400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>59500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>59300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>59000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>59500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>34400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>34300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>34200</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7348,117 +7537,123 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7466,103 +7661,106 @@
         <v>500</v>
       </c>
       <c r="E81" s="3">
+        <v>500</v>
+      </c>
+      <c r="F81" s="3">
         <v>700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>400</v>
-      </c>
-      <c r="J81" s="3">
-        <v>500</v>
       </c>
       <c r="K81" s="3">
         <v>500</v>
       </c>
       <c r="L81" s="3">
+        <v>500</v>
+      </c>
+      <c r="M81" s="3">
         <v>600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>400</v>
-      </c>
-      <c r="P81" s="3">
-        <v>500</v>
       </c>
       <c r="Q81" s="3">
         <v>500</v>
       </c>
       <c r="R81" s="3">
+        <v>500</v>
+      </c>
+      <c r="S81" s="3">
         <v>700</v>
-      </c>
-      <c r="S81" s="3">
-        <v>500</v>
       </c>
       <c r="T81" s="3">
         <v>500</v>
       </c>
       <c r="U81" s="3">
+        <v>500</v>
+      </c>
+      <c r="V81" s="3">
         <v>800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>500</v>
-      </c>
-      <c r="X81" s="3">
-        <v>400</v>
       </c>
       <c r="Y81" s="3">
         <v>400</v>
       </c>
       <c r="Z81" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AA81" s="3">
         <v>200</v>
       </c>
       <c r="AB81" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC81" s="3">
         <v>300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-400</v>
       </c>
-      <c r="AF81" s="3">
-        <v>0</v>
-      </c>
       <c r="AG81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH81" s="3">
         <v>100</v>
       </c>
       <c r="AI81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7599,8 +7797,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7616,8 +7815,8 @@
       <c r="G83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H83" s="3">
-        <v>100</v>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
@@ -7641,10 +7840,10 @@
         <v>100</v>
       </c>
       <c r="P83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="3">
         <v>200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>100</v>
@@ -7656,10 +7855,10 @@
         <v>100</v>
       </c>
       <c r="U83" s="3">
+        <v>100</v>
+      </c>
+      <c r="V83" s="3">
         <v>200</v>
-      </c>
-      <c r="V83" s="3">
-        <v>100</v>
       </c>
       <c r="W83" s="3">
         <v>100</v>
@@ -7703,8 +7902,11 @@
       <c r="AJ83" s="3">
         <v>100</v>
       </c>
+      <c r="AK83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7807,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7911,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8015,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8119,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8223,8 +8437,11 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8252,83 +8469,86 @@
       <c r="K89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
         <v>1300</v>
-      </c>
-      <c r="M89" s="3">
-        <v>900</v>
       </c>
       <c r="N89" s="3">
         <v>900</v>
       </c>
       <c r="O89" s="3">
+        <v>900</v>
+      </c>
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1000</v>
-      </c>
-      <c r="U89" s="3">
-        <v>1100</v>
       </c>
       <c r="V89" s="3">
         <v>1100</v>
       </c>
       <c r="W89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X89" s="3">
         <v>800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8365,8 +8585,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8394,8 +8615,8 @@
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8428,11 +8649,11 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
@@ -8452,25 +8673,28 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
       <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-200</v>
       </c>
-      <c r="AI91" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8573,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8677,8 +8904,11 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8706,83 +8936,86 @@
       <c r="K94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3">
         <v>-13300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>19100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>9600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>17000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>38400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-19300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>6200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>6700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>3100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8819,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8848,8 +9082,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8923,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9027,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9131,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9235,8 +9478,11 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9264,83 +9510,86 @@
       <c r="K100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
         <v>6800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-15800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-11000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>14900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>14000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-8000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-15800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>34100</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>4900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>4600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-12600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>33600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9368,8 +9617,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9443,8 +9692,11 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9473,78 +9725,81 @@
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-5200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-26300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>38600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>25300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>17600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>34000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-12200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-19800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-24500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>35200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-6800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-20400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>26400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2200</v>
       </c>
     </row>
